--- a/Inputs/idef.xlsx
+++ b/Inputs/idef.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sofia\Documents\BID\2025\calculo_indicators_R\Inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{767ABC9E-4A14-4BFD-BFB0-F778D430DDB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B75091E-F719-423D-AD8A-A0D4070DF87D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{76C58BDB-E763-4EA4-A4AF-6A5E1AEAFFAC}"/>
+    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="10240" xr2:uid="{76C58BDB-E763-4EA4-A4AF-6A5E1AEAFFAC}"/>
   </bookViews>
   <sheets>
     <sheet name="idef" sheetId="1" r:id="rId1"/>
@@ -151,9 +151,6 @@
     <t xml:space="preserve">asis_prim_c==1 </t>
   </si>
   <si>
-    <t>age_prim_c==1 &amp; (!is.na(asiste_ci)) &amp;  (!is.na(aedu_ci))</t>
-  </si>
-  <si>
     <t>tasa_bruta_asis_seco</t>
   </si>
   <si>
@@ -178,9 +175,6 @@
     <t>asis_net_prim_c==1</t>
   </si>
   <si>
-    <t>age_prim_c==1 &amp; (!is.na(asiste_ci)) &amp; (!is.na(aedu_ci))</t>
-  </si>
-  <si>
     <t>tasa_neta_asis_seco</t>
   </si>
   <si>
@@ -340,69 +334,33 @@
     <t>razonesnoasis_econ_12_17</t>
   </si>
   <si>
-    <t>razonesnoasis_ci==1 &amp; edad_ci &gt;=12 &amp; edad_ci &lt;=17 &amp; asiste_ci !=1 &amp; nivel_edu !=6</t>
-  </si>
-  <si>
-    <t>edad_ci&gt;=12 &amp; edad_ci&lt;=17 &amp; asiste_ci !=1 &amp; asiste_ci !=1 &amp; nivel_edu!=6 &amp; (!is.na(razonesnoasis_ci))</t>
-  </si>
-  <si>
     <t>razonesnoasis_interes_12_17</t>
   </si>
   <si>
-    <t>razonesnoasis_ci == 2 &amp; edad_ci &gt;= 12 &amp; edad_ci &lt;= 17  &amp; asiste_ci != 1 &amp; nivel_edu != 6</t>
-  </si>
-  <si>
     <t>razonesnoasis_cuidados_12_17</t>
   </si>
   <si>
-    <t>razonesnoasis_ci == 3 &amp; edad_ci &gt;= 12 &amp; edad_ci &lt;= 17  &amp; asiste_ci != 1 &amp; nivel_edu != 6</t>
-  </si>
-  <si>
     <t>razonesnoasis_acceso_12_17</t>
   </si>
   <si>
-    <t>razonesnoasis_ci == 4 &amp; edad_ci &gt;= 12 &amp; edad_ci &lt;= 17  &amp; asiste_ci != 1 &amp; nivel_edu != 6</t>
-  </si>
-  <si>
     <t>razonesnoasis_otros_12_17</t>
   </si>
   <si>
-    <t>razonesnoasis_ci == 5 &amp; edad_ci &gt;= 12 &amp; edad_ci &lt;= 17  &amp; asiste_ci != 1 &amp; nivel_edu != 6</t>
-  </si>
-  <si>
     <t>razonesnoasis_econ_18_24</t>
   </si>
   <si>
-    <t>razonesnoasis_ci==1 &amp; edad_ci &gt;=18 &amp; edad_ci &lt;=24 &amp; asiste_ci !=1 &amp; nivel_edu !=6</t>
-  </si>
-  <si>
-    <t>edad_ci&gt;=18 &amp; edad_ci&lt;=24 &amp; asiste_ci !=1 &amp; asiste_ci !=1 &amp; nivel_edu!=6 &amp; (!is.na(razonesnoasis_ci))</t>
-  </si>
-  <si>
     <t>razonesnoasis_interes_18_24</t>
   </si>
   <si>
-    <t>razonesnoasis_ci == 2 &amp; edad_ci &gt;= 18 &amp; edad_ci &lt;= 24 &amp; asiste_ci != 1 &amp; nivel_edu != 6</t>
-  </si>
-  <si>
     <t>razonesnoasis_cuidados_18_24</t>
   </si>
   <si>
-    <t>razonesnoasis_ci == 3 &amp; edad_ci &gt;= 18 &amp; edad_ci &lt;= 24 &amp; asiste_ci != 1 &amp; nivel_edu != 6</t>
-  </si>
-  <si>
     <t>razonesnoasis_acceso_18_24</t>
   </si>
   <si>
-    <t>razonesnoasis_ci == 4 &amp; edad_ci &gt;= 18 &amp; edad_ci &lt;= 24 &amp; asiste_ci != 1 &amp; nivel_edu != 6</t>
-  </si>
-  <si>
     <t>razonesnoasis_otros_18_24</t>
   </si>
   <si>
-    <t>razonesnoasis_ci == 5 &amp; edad_ci &gt;= 18 &amp; edad_ci &lt;= 24 &amp; asiste_ci != 1 &amp; nivel_edu != 6</t>
-  </si>
-  <si>
     <t>tasa_aban_12_17</t>
   </si>
   <si>
@@ -2048,6 +2006,48 @@
   </si>
   <si>
     <t>!is.na(aedupea_ci) &amp; aedupea_ci&lt;=25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">age_prim_c==1 &amp; (!is.na(asiste_ci)) </t>
+  </si>
+  <si>
+    <t>age_prim_c==1 &amp; (!is.na(asiste_ci))</t>
+  </si>
+  <si>
+    <t>edad_ci&gt;=12 &amp; edad_ci&lt;=17 &amp; asiste_ci !=1 &amp; asiste_ci !=1 &amp; nivel_edu&lt;6 &amp; (!is.na(razonesnoasis_ci))</t>
+  </si>
+  <si>
+    <t>edad_ci&gt;=18 &amp; edad_ci&lt;=24 &amp; asiste_ci !=1 &amp; asiste_ci !=1 &amp; nivel_edu&lt;6 &amp; (!is.na(razonesnoasis_ci))</t>
+  </si>
+  <si>
+    <t>razonesnoasis_ci==1 &amp; edad_ci &gt;=12 &amp; edad_ci &lt;=17 &amp; asiste_ci !=1 &amp; nivel_edu &lt;6</t>
+  </si>
+  <si>
+    <t>razonesnoasis_ci == 2 &amp; edad_ci &gt;= 12 &amp; edad_ci &lt;= 17  &amp; asiste_ci != 1 &amp; nivel_edu &lt; 6</t>
+  </si>
+  <si>
+    <t>razonesnoasis_ci == 3 &amp; edad_ci &gt;= 12 &amp; edad_ci &lt;= 17  &amp; asiste_ci != 1 &amp; nivel_edu &lt; 6</t>
+  </si>
+  <si>
+    <t>razonesnoasis_ci == 4 &amp; edad_ci &gt;= 12 &amp; edad_ci &lt;= 17  &amp; asiste_ci != 1 &amp; nivel_edu&lt; 6</t>
+  </si>
+  <si>
+    <t>razonesnoasis_ci == 5 &amp; edad_ci &gt;= 12 &amp; edad_ci &lt;= 17  &amp; asiste_ci != 1 &amp; nivel_edu &lt; 6</t>
+  </si>
+  <si>
+    <t>razonesnoasis_ci==1 &amp; edad_ci &gt;=18 &amp; edad_ci &lt;=24 &amp; asiste_ci !=1 &amp; nivel_edu&lt;6</t>
+  </si>
+  <si>
+    <t>razonesnoasis_ci == 2 &amp; edad_ci &gt;= 18 &amp; edad_ci &lt;= 24 &amp; asiste_ci != 1 &amp; nivel_edu&lt; 6</t>
+  </si>
+  <si>
+    <t>razonesnoasis_ci == 3 &amp; edad_ci &gt;= 18 &amp; edad_ci &lt;= 24 &amp; asiste_ci != 1 &amp; nivel_edu &lt; 6</t>
+  </si>
+  <si>
+    <t>razonesnoasis_ci == 5 &amp; edad_ci &gt;= 18 &amp; edad_ci &lt;= 24 &amp; asiste_ci != 1 &amp; nivel_edu &lt; 6</t>
+  </si>
+  <si>
+    <t>razonesnoasis_ci == 4 &amp; edad_ci &gt;= 18 &amp; edad_ci &lt;= 24 &amp; asiste_ci != 1 &amp; nivel_edu&lt; 6</t>
   </si>
 </sst>
 </file>
@@ -2968,10 +2968,10 @@
         <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>671</v>
+        <v>657</v>
       </c>
       <c r="E2" t="s">
-        <v>670</v>
+        <v>656</v>
       </c>
       <c r="F2" t="s">
         <v>12</v>
@@ -2997,7 +2997,7 @@
         <v>15</v>
       </c>
       <c r="E3" t="s">
-        <v>674</v>
+        <v>660</v>
       </c>
       <c r="F3" t="s">
         <v>12</v>
@@ -3023,7 +3023,7 @@
         <v>17</v>
       </c>
       <c r="E4" t="s">
-        <v>673</v>
+        <v>659</v>
       </c>
       <c r="F4" t="s">
         <v>12</v>
@@ -3049,7 +3049,7 @@
         <v>11</v>
       </c>
       <c r="E5" t="s">
-        <v>672</v>
+        <v>658</v>
       </c>
       <c r="F5" t="s">
         <v>12</v>
@@ -3101,7 +3101,7 @@
         <v>24</v>
       </c>
       <c r="E7" t="s">
-        <v>660</v>
+        <v>646</v>
       </c>
       <c r="F7" t="s">
         <v>12</v>
@@ -3257,7 +3257,7 @@
         <v>41</v>
       </c>
       <c r="E13" t="s">
-        <v>42</v>
+        <v>661</v>
       </c>
       <c r="F13" t="s">
         <v>12</v>
@@ -3271,7 +3271,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B14" t="s">
         <v>9</v>
@@ -3280,10 +3280,10 @@
         <v>20</v>
       </c>
       <c r="D14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" t="s">
         <v>44</v>
-      </c>
-      <c r="E14" t="s">
-        <v>45</v>
       </c>
       <c r="F14" t="s">
         <v>12</v>
@@ -3297,7 +3297,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B15" t="s">
         <v>9</v>
@@ -3306,10 +3306,10 @@
         <v>20</v>
       </c>
       <c r="D15" t="s">
+        <v>46</v>
+      </c>
+      <c r="E15" t="s">
         <v>47</v>
-      </c>
-      <c r="E15" t="s">
-        <v>48</v>
       </c>
       <c r="F15" t="s">
         <v>12</v>
@@ -3323,7 +3323,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B16" t="s">
         <v>9</v>
@@ -3332,10 +3332,10 @@
         <v>20</v>
       </c>
       <c r="D16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E16" t="s">
-        <v>51</v>
+        <v>662</v>
       </c>
       <c r="F16" t="s">
         <v>12</v>
@@ -3349,7 +3349,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B17" t="s">
         <v>9</v>
@@ -3358,10 +3358,10 @@
         <v>20</v>
       </c>
       <c r="D17" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F17" t="s">
         <v>12</v>
@@ -3375,7 +3375,7 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B18" t="s">
         <v>9</v>
@@ -3384,10 +3384,10 @@
         <v>20</v>
       </c>
       <c r="D18" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F18" t="s">
         <v>12</v>
@@ -3401,7 +3401,7 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B19" t="s">
         <v>9</v>
@@ -3410,10 +3410,10 @@
         <v>20</v>
       </c>
       <c r="D19" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E19" t="s">
-        <v>664</v>
+        <v>650</v>
       </c>
       <c r="F19" t="s">
         <v>12</v>
@@ -3427,7 +3427,7 @@
     </row>
     <row r="20" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
-        <v>652</v>
+        <v>638</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>9</v>
@@ -3436,10 +3436,10 @@
         <v>20</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>654</v>
+        <v>640</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>665</v>
+        <v>651</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>12</v>
@@ -3453,7 +3453,7 @@
     </row>
     <row r="21" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
-        <v>653</v>
+        <v>639</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>9</v>
@@ -3462,10 +3462,10 @@
         <v>20</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>655</v>
+        <v>641</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>666</v>
+        <v>652</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>12</v>
@@ -3479,7 +3479,7 @@
     </row>
     <row r="22" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
-        <v>667</v>
+        <v>653</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>9</v>
@@ -3488,10 +3488,10 @@
         <v>20</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>668</v>
+        <v>654</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>669</v>
+        <v>655</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>12</v>
@@ -3505,7 +3505,7 @@
     </row>
     <row r="23" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>9</v>
@@ -3514,10 +3514,10 @@
         <v>20</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>651</v>
+        <v>637</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>12</v>
@@ -3531,7 +3531,7 @@
     </row>
     <row r="24" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>9</v>
@@ -3540,10 +3540,10 @@
         <v>20</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>656</v>
+        <v>642</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>12</v>
@@ -3557,7 +3557,7 @@
     </row>
     <row r="25" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>9</v>
@@ -3566,10 +3566,10 @@
         <v>20</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>657</v>
+        <v>643</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>12</v>
@@ -3583,7 +3583,7 @@
     </row>
     <row r="26" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>9</v>
@@ -3592,10 +3592,10 @@
         <v>20</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>657</v>
+        <v>643</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>12</v>
@@ -3609,7 +3609,7 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B27" t="s">
         <v>9</v>
@@ -3618,16 +3618,16 @@
         <v>20</v>
       </c>
       <c r="D27" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E27" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F27" t="s">
         <v>12</v>
       </c>
       <c r="G27" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H27">
         <v>1</v>
@@ -3635,7 +3635,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B28" t="s">
         <v>9</v>
@@ -3644,16 +3644,16 @@
         <v>20</v>
       </c>
       <c r="D28" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E28" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F28" t="s">
         <v>12</v>
       </c>
       <c r="G28" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H28">
         <v>1</v>
@@ -3661,7 +3661,7 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B29" t="s">
         <v>9</v>
@@ -3670,10 +3670,10 @@
         <v>20</v>
       </c>
       <c r="D29" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E29" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F29" t="s">
         <v>12</v>
@@ -3687,7 +3687,7 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B30" t="s">
         <v>9</v>
@@ -3696,10 +3696,10 @@
         <v>20</v>
       </c>
       <c r="D30" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E30" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F30" t="s">
         <v>12</v>
@@ -3713,7 +3713,7 @@
     </row>
     <row r="31" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>9</v>
@@ -3722,10 +3722,10 @@
         <v>20</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>658</v>
+        <v>644</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>12</v>
@@ -3739,7 +3739,7 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B32" t="s">
         <v>9</v>
@@ -3748,10 +3748,10 @@
         <v>20</v>
       </c>
       <c r="D32" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E32" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F32" t="s">
         <v>12</v>
@@ -3765,7 +3765,7 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B33" t="s">
         <v>9</v>
@@ -3774,10 +3774,10 @@
         <v>20</v>
       </c>
       <c r="D33" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E33" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F33" t="s">
         <v>12</v>
@@ -3791,7 +3791,7 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B34" t="s">
         <v>9</v>
@@ -3800,10 +3800,10 @@
         <v>20</v>
       </c>
       <c r="D34" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E34" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F34" t="s">
         <v>12</v>
@@ -3817,7 +3817,7 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B35" t="s">
         <v>9</v>
@@ -3826,10 +3826,10 @@
         <v>20</v>
       </c>
       <c r="D35" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E35" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F35" t="s">
         <v>12</v>
@@ -3843,7 +3843,7 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B36" t="s">
         <v>9</v>
@@ -3852,10 +3852,10 @@
         <v>20</v>
       </c>
       <c r="D36" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E36" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F36" t="s">
         <v>12</v>
@@ -3869,7 +3869,7 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B37" t="s">
         <v>9</v>
@@ -3878,10 +3878,10 @@
         <v>20</v>
       </c>
       <c r="D37" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E37" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F37" t="s">
         <v>12</v>
@@ -3895,7 +3895,7 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B38" t="s">
         <v>9</v>
@@ -3904,10 +3904,10 @@
         <v>20</v>
       </c>
       <c r="D38" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E38" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F38" t="s">
         <v>12</v>
@@ -3921,7 +3921,7 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B39" t="s">
         <v>9</v>
@@ -3930,10 +3930,10 @@
         <v>20</v>
       </c>
       <c r="D39" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E39" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F39" t="s">
         <v>12</v>
@@ -3947,7 +3947,7 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B40" t="s">
         <v>9</v>
@@ -3956,10 +3956,10 @@
         <v>20</v>
       </c>
       <c r="D40" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E40" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F40" t="s">
         <v>12</v>
@@ -3973,7 +3973,7 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B41" t="s">
         <v>9</v>
@@ -3982,10 +3982,10 @@
         <v>20</v>
       </c>
       <c r="D41" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E41" t="s">
-        <v>661</v>
+        <v>647</v>
       </c>
       <c r="F41" t="s">
         <v>12</v>
@@ -3999,7 +3999,7 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B42" t="s">
         <v>9</v>
@@ -4008,10 +4008,10 @@
         <v>20</v>
       </c>
       <c r="D42" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E42" t="s">
-        <v>662</v>
+        <v>648</v>
       </c>
       <c r="F42" t="s">
         <v>12</v>
@@ -4025,7 +4025,7 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B43" t="s">
         <v>9</v>
@@ -4034,10 +4034,10 @@
         <v>20</v>
       </c>
       <c r="D43" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E43" t="s">
-        <v>663</v>
+        <v>649</v>
       </c>
       <c r="F43" t="s">
         <v>12</v>
@@ -4051,7 +4051,7 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B44" t="s">
         <v>9</v>
@@ -4060,10 +4060,10 @@
         <v>20</v>
       </c>
       <c r="D44" t="s">
-        <v>105</v>
+        <v>665</v>
       </c>
       <c r="E44" t="s">
-        <v>106</v>
+        <v>663</v>
       </c>
       <c r="F44" t="s">
         <v>12</v>
@@ -4077,7 +4077,7 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B45" t="s">
         <v>9</v>
@@ -4086,10 +4086,10 @@
         <v>20</v>
       </c>
       <c r="D45" t="s">
-        <v>108</v>
+        <v>666</v>
       </c>
       <c r="E45" t="s">
-        <v>106</v>
+        <v>663</v>
       </c>
       <c r="F45" t="s">
         <v>12</v>
@@ -4103,7 +4103,7 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B46" t="s">
         <v>9</v>
@@ -4112,10 +4112,10 @@
         <v>20</v>
       </c>
       <c r="D46" t="s">
-        <v>110</v>
+        <v>667</v>
       </c>
       <c r="E46" t="s">
-        <v>106</v>
+        <v>663</v>
       </c>
       <c r="F46" t="s">
         <v>12</v>
@@ -4129,7 +4129,7 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="B47" t="s">
         <v>9</v>
@@ -4138,10 +4138,10 @@
         <v>20</v>
       </c>
       <c r="D47" t="s">
-        <v>112</v>
+        <v>668</v>
       </c>
       <c r="E47" t="s">
-        <v>106</v>
+        <v>663</v>
       </c>
       <c r="F47" t="s">
         <v>12</v>
@@ -4155,7 +4155,7 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="B48" t="s">
         <v>9</v>
@@ -4164,10 +4164,10 @@
         <v>20</v>
       </c>
       <c r="D48" t="s">
-        <v>114</v>
+        <v>669</v>
       </c>
       <c r="E48" t="s">
-        <v>106</v>
+        <v>663</v>
       </c>
       <c r="F48" t="s">
         <v>12</v>
@@ -4181,7 +4181,7 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="B49" t="s">
         <v>9</v>
@@ -4190,10 +4190,10 @@
         <v>20</v>
       </c>
       <c r="D49" t="s">
-        <v>116</v>
+        <v>670</v>
       </c>
       <c r="E49" t="s">
-        <v>117</v>
+        <v>664</v>
       </c>
       <c r="F49" t="s">
         <v>12</v>
@@ -4207,7 +4207,7 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="B50" t="s">
         <v>9</v>
@@ -4216,10 +4216,10 @@
         <v>20</v>
       </c>
       <c r="D50" t="s">
-        <v>119</v>
+        <v>671</v>
       </c>
       <c r="E50" t="s">
-        <v>117</v>
+        <v>664</v>
       </c>
       <c r="F50" t="s">
         <v>12</v>
@@ -4233,7 +4233,7 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="B51" t="s">
         <v>9</v>
@@ -4242,10 +4242,10 @@
         <v>20</v>
       </c>
       <c r="D51" t="s">
-        <v>121</v>
+        <v>672</v>
       </c>
       <c r="E51" t="s">
-        <v>117</v>
+        <v>664</v>
       </c>
       <c r="F51" t="s">
         <v>12</v>
@@ -4259,7 +4259,7 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="B52" t="s">
         <v>9</v>
@@ -4268,10 +4268,10 @@
         <v>20</v>
       </c>
       <c r="D52" t="s">
-        <v>123</v>
+        <v>674</v>
       </c>
       <c r="E52" t="s">
-        <v>117</v>
+        <v>664</v>
       </c>
       <c r="F52" t="s">
         <v>12</v>
@@ -4285,7 +4285,7 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="B53" t="s">
         <v>9</v>
@@ -4294,10 +4294,10 @@
         <v>20</v>
       </c>
       <c r="D53" t="s">
-        <v>125</v>
+        <v>673</v>
       </c>
       <c r="E53" t="s">
-        <v>117</v>
+        <v>664</v>
       </c>
       <c r="F53" t="s">
         <v>12</v>
@@ -4311,7 +4311,7 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="B54" t="s">
         <v>9</v>
@@ -4320,10 +4320,10 @@
         <v>20</v>
       </c>
       <c r="D54" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="E54" t="s">
-        <v>659</v>
+        <v>645</v>
       </c>
       <c r="F54" t="s">
         <v>12</v>
@@ -4337,22 +4337,22 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="B55" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="C55" t="s">
         <v>20</v>
       </c>
       <c r="D55" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="E55" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="F55" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="G55" t="s">
         <v>13</v>
@@ -4363,22 +4363,22 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="B56" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="C56" t="s">
         <v>20</v>
       </c>
       <c r="D56" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="E56" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="F56" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="G56" t="s">
         <v>13</v>
@@ -4389,22 +4389,22 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="B57" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="C57" t="s">
         <v>20</v>
       </c>
       <c r="D57" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="E57" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="F57" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="G57" t="s">
         <v>13</v>
@@ -4415,22 +4415,22 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="B58" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="C58" t="s">
         <v>10</v>
       </c>
       <c r="D58" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="E58" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="F58" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="G58" t="s">
         <v>13</v>
@@ -4441,22 +4441,22 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="B59" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="C59" t="s">
         <v>20</v>
       </c>
       <c r="D59" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="E59" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="F59" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="G59" t="s">
         <v>13</v>
@@ -4467,22 +4467,22 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="B60" t="s">
+        <v>115</v>
+      </c>
+      <c r="C60" t="s">
+        <v>20</v>
+      </c>
+      <c r="D60" t="s">
         <v>129</v>
       </c>
-      <c r="C60" t="s">
-        <v>20</v>
-      </c>
-      <c r="D60" t="s">
-        <v>143</v>
-      </c>
       <c r="E60" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="F60" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="G60" t="s">
         <v>13</v>
@@ -4493,22 +4493,22 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="B61" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="C61" t="s">
         <v>20</v>
       </c>
       <c r="D61" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="E61" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="F61" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="G61" t="s">
         <v>13</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="B62" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="C62" t="s">
         <v>20</v>
       </c>
       <c r="D62" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="E62" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="F62" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="G62" t="s">
         <v>13</v>
@@ -4545,22 +4545,22 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="B63" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="C63" t="s">
         <v>20</v>
       </c>
       <c r="D63" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="E63" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="F63" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="G63" t="s">
         <v>13</v>
@@ -4571,22 +4571,22 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="B64" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="C64" t="s">
         <v>20</v>
       </c>
       <c r="D64" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="E64" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="F64" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="G64" t="s">
         <v>13</v>
@@ -4597,22 +4597,22 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="B65" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="C65" t="s">
         <v>20</v>
       </c>
       <c r="D65" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="E65" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="F65" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="G65" t="s">
         <v>13</v>
@@ -4623,19 +4623,19 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="B66" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="C66" t="s">
         <v>20</v>
       </c>
       <c r="D66" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="E66" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="F66" t="s">
         <v>12</v>
@@ -4649,22 +4649,22 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="B67" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="C67" t="s">
         <v>10</v>
       </c>
       <c r="D67" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="E67" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="F67" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="G67" t="s">
         <v>13</v>
@@ -4675,22 +4675,22 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="B68" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="C68" t="s">
         <v>20</v>
       </c>
       <c r="D68" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="E68" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="F68" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="G68" t="s">
         <v>13</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="B69" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="C69" t="s">
         <v>20</v>
       </c>
       <c r="D69" t="s">
-        <v>169</v>
+        <v>155</v>
       </c>
       <c r="E69" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="F69" t="s">
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="G69" t="s">
         <v>13</v>
@@ -4727,22 +4727,22 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="B70" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="C70" t="s">
         <v>20</v>
       </c>
       <c r="D70" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="E70" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="F70" t="s">
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="G70" t="s">
         <v>13</v>
@@ -4753,22 +4753,22 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="B71" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="C71" t="s">
         <v>10</v>
       </c>
       <c r="D71" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="E71" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="F71" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="G71" t="s">
         <v>13</v>
@@ -4779,22 +4779,22 @@
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="B72" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="C72" t="s">
         <v>20</v>
       </c>
       <c r="D72" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="E72" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="F72" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="G72" t="s">
         <v>13</v>
@@ -4805,22 +4805,22 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="B73" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="C73" t="s">
         <v>20</v>
       </c>
       <c r="D73" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="E73" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="F73" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="G73" t="s">
         <v>13</v>
@@ -4831,19 +4831,19 @@
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="B74" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="C74" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="D74" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="E74" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="F74" t="s">
         <v>12</v>
@@ -4857,19 +4857,19 @@
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="B75" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="C75" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="D75" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="E75" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="F75" t="s">
         <v>12</v>
@@ -4883,19 +4883,19 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="B76" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="C76" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="D76" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="E76" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="F76" t="s">
         <v>12</v>
@@ -4909,19 +4909,19 @@
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="B77" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="C77" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="D77" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="E77" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="F77" t="s">
         <v>12</v>
@@ -4935,19 +4935,19 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="B78" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="C78" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="D78" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="E78" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="F78" t="s">
         <v>12</v>
@@ -4961,19 +4961,19 @@
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="B79" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="C79" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="D79" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="E79" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="F79" t="s">
         <v>12</v>
@@ -4987,25 +4987,25 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="B80" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="C80" t="s">
         <v>20</v>
       </c>
       <c r="D80" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
       <c r="E80" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="F80" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="G80" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H80">
         <v>1</v>
@@ -5013,25 +5013,25 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="B81" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="C81" t="s">
         <v>20</v>
       </c>
       <c r="D81" t="s">
-        <v>201</v>
+        <v>187</v>
       </c>
       <c r="E81" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="F81" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="G81" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H81">
         <v>1</v>
@@ -5039,25 +5039,25 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="B82" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="C82" t="s">
         <v>20</v>
       </c>
       <c r="D82" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="E82" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="F82" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="G82" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H82">
         <v>1</v>
@@ -5065,25 +5065,25 @@
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="B83" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="C83" t="s">
         <v>20</v>
       </c>
       <c r="D83" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="E83" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="F83" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="G83" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H83">
         <v>1</v>
@@ -5091,25 +5091,25 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="B84" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="C84" t="s">
         <v>20</v>
       </c>
       <c r="D84" t="s">
-        <v>208</v>
+        <v>194</v>
       </c>
       <c r="E84" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="F84" t="s">
-        <v>210</v>
+        <v>196</v>
       </c>
       <c r="G84" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H84">
         <v>0</v>
@@ -5117,25 +5117,25 @@
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="B85" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="C85" t="s">
         <v>20</v>
       </c>
       <c r="D85" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="E85" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="F85" t="s">
-        <v>210</v>
+        <v>196</v>
       </c>
       <c r="G85" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H85">
         <v>0</v>
@@ -5143,25 +5143,25 @@
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="B86" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="C86" t="s">
         <v>20</v>
       </c>
       <c r="D86" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="E86" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="F86" t="s">
-        <v>210</v>
+        <v>196</v>
       </c>
       <c r="G86" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H86">
         <v>0</v>
@@ -5169,25 +5169,25 @@
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="B87" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="C87" t="s">
         <v>20</v>
       </c>
       <c r="D87" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="E87" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="F87" t="s">
-        <v>210</v>
+        <v>196</v>
       </c>
       <c r="G87" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H87">
         <v>0</v>
@@ -5195,25 +5195,25 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="B88" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C88" t="s">
         <v>10</v>
       </c>
       <c r="D88" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="E88" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="F88" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G88" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H88">
         <v>0</v>
@@ -5221,25 +5221,25 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>223</v>
+        <v>209</v>
       </c>
       <c r="B89" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C89" t="s">
         <v>20</v>
       </c>
       <c r="D89" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="E89" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="F89" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G89" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H89">
         <v>1</v>
@@ -5247,25 +5247,25 @@
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>226</v>
+        <v>212</v>
       </c>
       <c r="B90" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C90" t="s">
         <v>20</v>
       </c>
       <c r="D90" t="s">
-        <v>227</v>
+        <v>213</v>
       </c>
       <c r="E90" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="F90" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G90" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H90">
         <v>0</v>
@@ -5273,25 +5273,25 @@
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="B91" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C91" t="s">
         <v>20</v>
       </c>
       <c r="D91" t="s">
-        <v>227</v>
+        <v>213</v>
       </c>
       <c r="E91" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="F91" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G91" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H91">
         <v>0</v>
@@ -5299,25 +5299,25 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="B92" t="s">
+        <v>204</v>
+      </c>
+      <c r="C92" t="s">
+        <v>20</v>
+      </c>
+      <c r="D92" t="s">
+        <v>217</v>
+      </c>
+      <c r="E92" t="s">
         <v>218</v>
       </c>
-      <c r="C92" t="s">
-        <v>20</v>
-      </c>
-      <c r="D92" t="s">
-        <v>231</v>
-      </c>
-      <c r="E92" t="s">
-        <v>232</v>
-      </c>
       <c r="F92" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G92" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H92">
         <v>0</v>
@@ -5325,25 +5325,25 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="B93" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C93" t="s">
         <v>20</v>
       </c>
       <c r="D93" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="E93" t="s">
-        <v>235</v>
+        <v>221</v>
       </c>
       <c r="F93" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G93" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H93">
         <v>0</v>
@@ -5351,25 +5351,25 @@
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>236</v>
+        <v>222</v>
       </c>
       <c r="B94" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C94" t="s">
         <v>10</v>
       </c>
       <c r="D94" t="s">
-        <v>237</v>
+        <v>223</v>
       </c>
       <c r="E94" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="F94" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G94" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H94">
         <v>0</v>
@@ -5377,25 +5377,25 @@
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>239</v>
+        <v>225</v>
       </c>
       <c r="B95" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C95" t="s">
         <v>10</v>
       </c>
       <c r="D95" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
       <c r="E95" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="F95" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G95" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H95">
         <v>0</v>
@@ -5403,25 +5403,25 @@
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="B96" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C96" t="s">
         <v>10</v>
       </c>
       <c r="D96" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
       <c r="E96" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="F96" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G96" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H96">
         <v>0</v>
@@ -5429,25 +5429,25 @@
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>244</v>
+        <v>230</v>
       </c>
       <c r="B97" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C97" t="s">
         <v>10</v>
       </c>
       <c r="D97" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="E97" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="F97" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G97" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H97">
         <v>0</v>
@@ -5455,25 +5455,25 @@
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="B98" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C98" t="s">
         <v>10</v>
       </c>
       <c r="D98" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="E98" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="F98" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G98" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H98">
         <v>0</v>
@@ -5481,25 +5481,25 @@
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="B99" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C99" t="s">
         <v>10</v>
       </c>
       <c r="D99" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="E99" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="F99" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G99" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H99">
         <v>0</v>
@@ -5507,25 +5507,25 @@
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
       <c r="B100" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C100" t="s">
         <v>10</v>
       </c>
       <c r="D100" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="E100" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="F100" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G100" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H100">
         <v>0</v>
@@ -5533,25 +5533,25 @@
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>250</v>
+        <v>236</v>
       </c>
       <c r="B101" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C101" t="s">
         <v>10</v>
       </c>
       <c r="D101" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="E101" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="F101" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G101" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H101">
         <v>0</v>
@@ -5559,25 +5559,25 @@
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B102" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C102" t="s">
         <v>10</v>
       </c>
       <c r="D102" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="E102" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="F102" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G102" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H102">
         <v>0</v>
@@ -5585,25 +5585,25 @@
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="B103" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C103" t="s">
         <v>10</v>
       </c>
       <c r="D103" t="s">
-        <v>257</v>
+        <v>243</v>
       </c>
       <c r="E103" t="s">
-        <v>258</v>
+        <v>244</v>
       </c>
       <c r="F103" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G103" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H103">
         <v>1</v>
@@ -5611,25 +5611,25 @@
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>259</v>
+        <v>245</v>
       </c>
       <c r="B104" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C104" t="s">
         <v>10</v>
       </c>
       <c r="D104" t="s">
-        <v>260</v>
+        <v>246</v>
       </c>
       <c r="E104" t="s">
-        <v>258</v>
+        <v>244</v>
       </c>
       <c r="F104" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G104" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H104">
         <v>0</v>
@@ -5637,25 +5637,25 @@
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="B105" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C105" t="s">
         <v>10</v>
       </c>
       <c r="D105" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="E105" t="s">
-        <v>258</v>
+        <v>244</v>
       </c>
       <c r="F105" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G105" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H105">
         <v>0</v>
@@ -5663,25 +5663,25 @@
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>263</v>
+        <v>249</v>
       </c>
       <c r="B106" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C106" t="s">
         <v>10</v>
       </c>
       <c r="D106" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
       <c r="E106" t="s">
-        <v>264</v>
+        <v>250</v>
       </c>
       <c r="F106" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G106" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H106">
         <v>0</v>
@@ -5689,25 +5689,25 @@
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="B107" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C107" t="s">
         <v>10</v>
       </c>
       <c r="D107" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="E107" t="s">
-        <v>264</v>
+        <v>250</v>
       </c>
       <c r="F107" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G107" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H107">
         <v>0</v>
@@ -5715,25 +5715,25 @@
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>266</v>
+        <v>252</v>
       </c>
       <c r="B108" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C108" t="s">
         <v>10</v>
       </c>
       <c r="D108" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="E108" t="s">
-        <v>264</v>
+        <v>250</v>
       </c>
       <c r="F108" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G108" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H108">
         <v>0</v>
@@ -5741,25 +5741,25 @@
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>267</v>
+        <v>253</v>
       </c>
       <c r="B109" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C109" t="s">
         <v>20</v>
       </c>
       <c r="D109" t="s">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="E109" t="s">
-        <v>269</v>
+        <v>255</v>
       </c>
       <c r="F109" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G109" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H109">
         <v>0</v>
@@ -5767,25 +5767,25 @@
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>270</v>
+        <v>256</v>
       </c>
       <c r="B110" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C110" t="s">
         <v>20</v>
       </c>
       <c r="D110" t="s">
-        <v>271</v>
+        <v>257</v>
       </c>
       <c r="E110" t="s">
-        <v>272</v>
+        <v>258</v>
       </c>
       <c r="F110" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G110" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H110">
         <v>0</v>
@@ -5793,25 +5793,25 @@
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>273</v>
+        <v>259</v>
       </c>
       <c r="B111" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C111" t="s">
         <v>20</v>
       </c>
       <c r="D111" t="s">
-        <v>274</v>
+        <v>260</v>
       </c>
       <c r="E111" t="s">
-        <v>272</v>
+        <v>258</v>
       </c>
       <c r="F111" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G111" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H111">
         <v>0</v>
@@ -5819,25 +5819,25 @@
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>275</v>
+        <v>261</v>
       </c>
       <c r="B112" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C112" t="s">
         <v>20</v>
       </c>
       <c r="D112" t="s">
-        <v>276</v>
+        <v>262</v>
       </c>
       <c r="E112" t="s">
-        <v>272</v>
+        <v>258</v>
       </c>
       <c r="F112" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G112" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H112">
         <v>0</v>
@@ -5845,25 +5845,25 @@
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>277</v>
+        <v>263</v>
       </c>
       <c r="B113" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C113" t="s">
         <v>20</v>
       </c>
       <c r="D113" t="s">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="E113" t="s">
-        <v>279</v>
+        <v>265</v>
       </c>
       <c r="F113" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G113" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H113">
         <v>0</v>
@@ -5871,25 +5871,25 @@
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>280</v>
+        <v>266</v>
       </c>
       <c r="B114" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C114" t="s">
         <v>20</v>
       </c>
       <c r="D114" t="s">
-        <v>281</v>
+        <v>267</v>
       </c>
       <c r="E114" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="F114" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G114" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H114">
         <v>0</v>
@@ -5897,25 +5897,25 @@
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>282</v>
+        <v>268</v>
       </c>
       <c r="B115" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C115" t="s">
         <v>10</v>
       </c>
       <c r="D115" t="s">
-        <v>283</v>
+        <v>269</v>
       </c>
       <c r="E115" t="s">
-        <v>284</v>
+        <v>270</v>
       </c>
       <c r="F115" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G115" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H115">
         <v>0</v>
@@ -5923,25 +5923,25 @@
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>285</v>
+        <v>271</v>
       </c>
       <c r="B116" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C116" t="s">
         <v>10</v>
       </c>
       <c r="D116" t="s">
-        <v>286</v>
+        <v>272</v>
       </c>
       <c r="E116" t="s">
-        <v>287</v>
+        <v>273</v>
       </c>
       <c r="F116" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G116" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H116">
         <v>0</v>
@@ -5949,25 +5949,25 @@
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>288</v>
+        <v>274</v>
       </c>
       <c r="B117" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C117" t="s">
         <v>10</v>
       </c>
       <c r="D117" t="s">
-        <v>289</v>
+        <v>275</v>
       </c>
       <c r="E117" t="s">
-        <v>290</v>
+        <v>276</v>
       </c>
       <c r="F117" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G117" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H117">
         <v>0</v>
@@ -5975,25 +5975,25 @@
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="B118" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C118" t="s">
         <v>10</v>
       </c>
       <c r="D118" t="s">
-        <v>292</v>
+        <v>278</v>
       </c>
       <c r="E118" t="s">
-        <v>290</v>
+        <v>276</v>
       </c>
       <c r="F118" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G118" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H118">
         <v>0</v>
@@ -6001,25 +6001,25 @@
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>293</v>
+        <v>279</v>
       </c>
       <c r="B119" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C119" t="s">
         <v>10</v>
       </c>
       <c r="D119" t="s">
-        <v>294</v>
+        <v>280</v>
       </c>
       <c r="E119" t="s">
-        <v>295</v>
+        <v>281</v>
       </c>
       <c r="F119" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G119" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H119">
         <v>0</v>
@@ -6027,25 +6027,25 @@
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>296</v>
+        <v>282</v>
       </c>
       <c r="B120" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C120" t="s">
         <v>10</v>
       </c>
       <c r="D120" t="s">
-        <v>297</v>
+        <v>283</v>
       </c>
       <c r="E120" t="s">
-        <v>295</v>
+        <v>281</v>
       </c>
       <c r="F120" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G120" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H120">
         <v>0</v>
@@ -6053,25 +6053,25 @@
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>298</v>
+        <v>284</v>
       </c>
       <c r="B121" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C121" t="s">
         <v>20</v>
       </c>
       <c r="D121" t="s">
-        <v>299</v>
+        <v>285</v>
       </c>
       <c r="E121" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="F121" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G121" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H121">
         <v>0</v>
@@ -6079,25 +6079,25 @@
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>300</v>
+        <v>286</v>
       </c>
       <c r="B122" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C122" t="s">
         <v>20</v>
       </c>
       <c r="D122" t="s">
-        <v>301</v>
+        <v>287</v>
       </c>
       <c r="E122" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="F122" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G122" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H122">
         <v>0</v>
@@ -6105,25 +6105,25 @@
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>302</v>
+        <v>288</v>
       </c>
       <c r="B123" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C123" t="s">
         <v>20</v>
       </c>
       <c r="D123" t="s">
-        <v>303</v>
+        <v>289</v>
       </c>
       <c r="E123" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="F123" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G123" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H123">
         <v>0</v>
@@ -6131,25 +6131,25 @@
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>304</v>
+        <v>290</v>
       </c>
       <c r="B124" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C124" t="s">
         <v>20</v>
       </c>
       <c r="D124" t="s">
-        <v>305</v>
+        <v>291</v>
       </c>
       <c r="E124" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="F124" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G124" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H124">
         <v>1</v>
@@ -6157,25 +6157,25 @@
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>306</v>
+        <v>292</v>
       </c>
       <c r="B125" t="s">
+        <v>204</v>
+      </c>
+      <c r="C125" t="s">
+        <v>20</v>
+      </c>
+      <c r="D125" t="s">
+        <v>293</v>
+      </c>
+      <c r="E125" t="s">
         <v>218</v>
       </c>
-      <c r="C125" t="s">
-        <v>20</v>
-      </c>
-      <c r="D125" t="s">
-        <v>307</v>
-      </c>
-      <c r="E125" t="s">
-        <v>232</v>
-      </c>
       <c r="F125" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G125" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H125">
         <v>0</v>
@@ -6183,25 +6183,25 @@
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>308</v>
+        <v>294</v>
       </c>
       <c r="B126" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C126" t="s">
         <v>20</v>
       </c>
       <c r="D126" t="s">
-        <v>309</v>
+        <v>295</v>
       </c>
       <c r="E126" t="s">
-        <v>310</v>
+        <v>296</v>
       </c>
       <c r="F126" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G126" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H126">
         <v>0</v>
@@ -6209,25 +6209,25 @@
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>311</v>
+        <v>297</v>
       </c>
       <c r="B127" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C127" t="s">
         <v>20</v>
       </c>
       <c r="D127" t="s">
-        <v>312</v>
+        <v>298</v>
       </c>
       <c r="E127" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="F127" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G127" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H127">
         <v>0</v>
@@ -6235,25 +6235,25 @@
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>313</v>
+        <v>299</v>
       </c>
       <c r="B128" t="s">
+        <v>204</v>
+      </c>
+      <c r="C128" t="s">
+        <v>20</v>
+      </c>
+      <c r="D128" t="s">
+        <v>300</v>
+      </c>
+      <c r="E128" t="s">
         <v>218</v>
       </c>
-      <c r="C128" t="s">
-        <v>20</v>
-      </c>
-      <c r="D128" t="s">
-        <v>314</v>
-      </c>
-      <c r="E128" t="s">
-        <v>232</v>
-      </c>
       <c r="F128" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G128" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H128">
         <v>0</v>
@@ -6261,25 +6261,25 @@
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>315</v>
+        <v>301</v>
       </c>
       <c r="B129" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C129" t="s">
         <v>20</v>
       </c>
       <c r="D129" t="s">
-        <v>316</v>
+        <v>302</v>
       </c>
       <c r="E129" t="s">
-        <v>235</v>
+        <v>221</v>
       </c>
       <c r="F129" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G129" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H129">
         <v>0</v>
@@ -6287,25 +6287,25 @@
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>317</v>
+        <v>303</v>
       </c>
       <c r="B130" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C130" t="s">
         <v>20</v>
       </c>
       <c r="D130" t="s">
-        <v>318</v>
+        <v>304</v>
       </c>
       <c r="E130" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="F130" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G130" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H130">
         <v>0</v>
@@ -6313,25 +6313,25 @@
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>319</v>
+        <v>305</v>
       </c>
       <c r="B131" t="s">
+        <v>204</v>
+      </c>
+      <c r="C131" t="s">
+        <v>20</v>
+      </c>
+      <c r="D131" t="s">
+        <v>306</v>
+      </c>
+      <c r="E131" t="s">
         <v>218</v>
       </c>
-      <c r="C131" t="s">
-        <v>20</v>
-      </c>
-      <c r="D131" t="s">
-        <v>320</v>
-      </c>
-      <c r="E131" t="s">
-        <v>232</v>
-      </c>
       <c r="F131" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G131" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H131">
         <v>0</v>
@@ -6339,25 +6339,25 @@
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>321</v>
+        <v>307</v>
       </c>
       <c r="B132" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C132" t="s">
         <v>20</v>
       </c>
       <c r="D132" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="E132" t="s">
-        <v>235</v>
+        <v>221</v>
       </c>
       <c r="F132" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G132" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H132">
         <v>0</v>
@@ -6365,25 +6365,25 @@
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>323</v>
+        <v>309</v>
       </c>
       <c r="B133" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C133" t="s">
         <v>20</v>
       </c>
       <c r="D133" t="s">
-        <v>324</v>
+        <v>310</v>
       </c>
       <c r="E133" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="F133" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G133" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H133">
         <v>0</v>
@@ -6391,25 +6391,25 @@
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>325</v>
+        <v>311</v>
       </c>
       <c r="B134" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C134" t="s">
         <v>20</v>
       </c>
       <c r="D134" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="E134" t="s">
-        <v>327</v>
+        <v>313</v>
       </c>
       <c r="F134" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G134" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H134">
         <v>0</v>
@@ -6417,25 +6417,25 @@
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="B135" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C135" t="s">
         <v>20</v>
       </c>
       <c r="D135" t="s">
-        <v>329</v>
+        <v>315</v>
       </c>
       <c r="E135" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="F135" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G135" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H135">
         <v>1</v>
@@ -6443,25 +6443,25 @@
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>330</v>
+        <v>316</v>
       </c>
       <c r="B136" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C136" t="s">
         <v>20</v>
       </c>
       <c r="D136" t="s">
-        <v>331</v>
+        <v>317</v>
       </c>
       <c r="E136" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="F136" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G136" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H136">
         <v>0</v>
@@ -6469,25 +6469,25 @@
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>332</v>
+        <v>318</v>
       </c>
       <c r="B137" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C137" t="s">
         <v>20</v>
       </c>
       <c r="D137" t="s">
-        <v>333</v>
+        <v>319</v>
       </c>
       <c r="E137" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="F137" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G137" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H137">
         <v>1</v>
@@ -6495,25 +6495,25 @@
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>334</v>
+        <v>320</v>
       </c>
       <c r="B138" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C138" t="s">
         <v>20</v>
       </c>
       <c r="D138" t="s">
-        <v>335</v>
+        <v>321</v>
       </c>
       <c r="E138" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="F138" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G138" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H138">
         <v>1</v>
@@ -6521,25 +6521,25 @@
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>336</v>
+        <v>322</v>
       </c>
       <c r="B139" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C139" t="s">
         <v>20</v>
       </c>
       <c r="D139" t="s">
-        <v>337</v>
+        <v>323</v>
       </c>
       <c r="E139" t="s">
-        <v>338</v>
+        <v>324</v>
       </c>
       <c r="F139" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G139" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H139">
         <v>0</v>
@@ -6547,25 +6547,25 @@
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>339</v>
+        <v>325</v>
       </c>
       <c r="B140" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C140" t="s">
         <v>20</v>
       </c>
       <c r="D140" t="s">
-        <v>340</v>
+        <v>326</v>
       </c>
       <c r="E140" t="s">
-        <v>338</v>
+        <v>324</v>
       </c>
       <c r="F140" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G140" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H140">
         <v>0</v>
@@ -6573,25 +6573,25 @@
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>341</v>
+        <v>327</v>
       </c>
       <c r="B141" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C141" t="s">
         <v>20</v>
       </c>
       <c r="D141" t="s">
-        <v>342</v>
+        <v>328</v>
       </c>
       <c r="E141" t="s">
-        <v>338</v>
+        <v>324</v>
       </c>
       <c r="F141" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G141" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H141">
         <v>0</v>
@@ -6599,25 +6599,25 @@
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>343</v>
+        <v>329</v>
       </c>
       <c r="B142" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C142" t="s">
         <v>20</v>
       </c>
       <c r="D142" t="s">
-        <v>344</v>
+        <v>330</v>
       </c>
       <c r="E142" t="s">
-        <v>327</v>
+        <v>313</v>
       </c>
       <c r="F142" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G142" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H142">
         <v>0</v>
@@ -6625,25 +6625,25 @@
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>345</v>
+        <v>331</v>
       </c>
       <c r="B143" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C143" t="s">
         <v>20</v>
       </c>
       <c r="D143" t="s">
-        <v>346</v>
+        <v>332</v>
       </c>
       <c r="E143" t="s">
-        <v>347</v>
+        <v>333</v>
       </c>
       <c r="F143" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G143" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H143">
         <v>0</v>
@@ -6651,25 +6651,25 @@
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>348</v>
+        <v>334</v>
       </c>
       <c r="B144" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C144" t="s">
         <v>20</v>
       </c>
       <c r="D144" t="s">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="E144" t="s">
-        <v>350</v>
+        <v>336</v>
       </c>
       <c r="F144" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G144" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H144">
         <v>0</v>
@@ -6677,25 +6677,25 @@
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>351</v>
+        <v>337</v>
       </c>
       <c r="B145" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C145" t="s">
         <v>20</v>
       </c>
       <c r="D145" t="s">
-        <v>352</v>
+        <v>338</v>
       </c>
       <c r="E145" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="F145" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G145" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H145">
         <v>0</v>
@@ -6703,25 +6703,25 @@
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>353</v>
+        <v>339</v>
       </c>
       <c r="B146" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C146" t="s">
         <v>20</v>
       </c>
       <c r="D146" t="s">
-        <v>350</v>
+        <v>336</v>
       </c>
       <c r="E146" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="F146" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G146" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H146">
         <v>1</v>
@@ -6729,25 +6729,25 @@
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>354</v>
+        <v>340</v>
       </c>
       <c r="B147" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C147" t="s">
         <v>20</v>
       </c>
       <c r="D147" t="s">
-        <v>355</v>
+        <v>341</v>
       </c>
       <c r="E147" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="F147" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G147" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H147">
         <v>0</v>
@@ -6755,25 +6755,25 @@
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>356</v>
+        <v>342</v>
       </c>
       <c r="B148" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C148" t="s">
         <v>20</v>
       </c>
       <c r="D148" t="s">
-        <v>357</v>
+        <v>343</v>
       </c>
       <c r="E148" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="F148" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G148" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H148">
         <v>0</v>
@@ -6781,25 +6781,25 @@
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>358</v>
+        <v>344</v>
       </c>
       <c r="B149" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C149" t="s">
         <v>20</v>
       </c>
       <c r="D149" t="s">
-        <v>359</v>
+        <v>345</v>
       </c>
       <c r="E149" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="F149" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G149" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H149">
         <v>1</v>
@@ -6807,25 +6807,25 @@
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>360</v>
+        <v>346</v>
       </c>
       <c r="B150" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C150" t="s">
         <v>20</v>
       </c>
       <c r="D150" t="s">
-        <v>361</v>
+        <v>347</v>
       </c>
       <c r="E150" t="s">
-        <v>362</v>
+        <v>348</v>
       </c>
       <c r="F150" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G150" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H150">
         <v>0</v>
@@ -6833,25 +6833,25 @@
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>363</v>
+        <v>349</v>
       </c>
       <c r="B151" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C151" t="s">
         <v>20</v>
       </c>
       <c r="D151" t="s">
-        <v>364</v>
+        <v>350</v>
       </c>
       <c r="E151" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="F151" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G151" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H151">
         <v>1</v>
@@ -6859,25 +6859,25 @@
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>365</v>
+        <v>351</v>
       </c>
       <c r="B152" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C152" t="s">
         <v>20</v>
       </c>
       <c r="D152" t="s">
-        <v>366</v>
+        <v>352</v>
       </c>
       <c r="E152" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="F152" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G152" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H152">
         <v>1</v>
@@ -6885,25 +6885,25 @@
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>367</v>
+        <v>353</v>
       </c>
       <c r="B153" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C153" t="s">
         <v>20</v>
       </c>
       <c r="D153" t="s">
-        <v>368</v>
+        <v>354</v>
       </c>
       <c r="E153" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="F153" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G153" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H153">
         <v>1</v>
@@ -6911,25 +6911,25 @@
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>369</v>
+        <v>355</v>
       </c>
       <c r="B154" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C154" t="s">
         <v>20</v>
       </c>
       <c r="D154" t="s">
-        <v>370</v>
+        <v>356</v>
       </c>
       <c r="E154" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="F154" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G154" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H154">
         <v>0</v>
@@ -6937,25 +6937,25 @@
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>371</v>
+        <v>357</v>
       </c>
       <c r="B155" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C155" t="s">
         <v>20</v>
       </c>
       <c r="D155" t="s">
-        <v>372</v>
+        <v>358</v>
       </c>
       <c r="E155" t="s">
-        <v>362</v>
+        <v>348</v>
       </c>
       <c r="F155" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G155" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H155">
         <v>1</v>
@@ -6963,25 +6963,25 @@
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>373</v>
+        <v>359</v>
       </c>
       <c r="B156" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C156" t="s">
         <v>20</v>
       </c>
       <c r="D156" t="s">
-        <v>374</v>
+        <v>360</v>
       </c>
       <c r="E156" t="s">
-        <v>375</v>
+        <v>361</v>
       </c>
       <c r="F156" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G156" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H156">
         <v>0</v>
@@ -6989,25 +6989,25 @@
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>376</v>
+        <v>362</v>
       </c>
       <c r="B157" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C157" t="s">
         <v>20</v>
       </c>
       <c r="D157" t="s">
-        <v>377</v>
+        <v>363</v>
       </c>
       <c r="E157" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="F157" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G157" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H157">
         <v>0</v>
@@ -7015,25 +7015,25 @@
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>378</v>
+        <v>364</v>
       </c>
       <c r="B158" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C158" t="s">
         <v>20</v>
       </c>
       <c r="D158" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="E158" t="s">
-        <v>379</v>
+        <v>365</v>
       </c>
       <c r="F158" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G158" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H158">
         <v>1</v>
@@ -7041,25 +7041,25 @@
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>380</v>
+        <v>366</v>
       </c>
       <c r="B159" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C159" t="s">
         <v>20</v>
       </c>
       <c r="D159" t="s">
-        <v>381</v>
+        <v>367</v>
       </c>
       <c r="E159" t="s">
-        <v>327</v>
+        <v>313</v>
       </c>
       <c r="F159" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G159" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H159">
         <v>0</v>
@@ -7067,25 +7067,25 @@
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>382</v>
+        <v>368</v>
       </c>
       <c r="B160" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C160" t="s">
         <v>20</v>
       </c>
       <c r="D160" t="s">
-        <v>383</v>
+        <v>369</v>
       </c>
       <c r="E160" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="F160" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G160" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H160">
         <v>1</v>
@@ -7093,25 +7093,25 @@
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>384</v>
+        <v>370</v>
       </c>
       <c r="B161" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C161" t="s">
         <v>20</v>
       </c>
       <c r="D161" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="E161" t="s">
-        <v>385</v>
+        <v>371</v>
       </c>
       <c r="F161" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G161" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H161">
         <v>0</v>
@@ -7119,25 +7119,25 @@
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>386</v>
+        <v>372</v>
       </c>
       <c r="B162" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C162" t="s">
         <v>20</v>
       </c>
       <c r="D162" t="s">
-        <v>387</v>
+        <v>373</v>
       </c>
       <c r="E162" t="s">
-        <v>272</v>
+        <v>258</v>
       </c>
       <c r="F162" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G162" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H162">
         <v>0</v>
@@ -7145,25 +7145,25 @@
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>388</v>
+        <v>374</v>
       </c>
       <c r="B163" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C163" t="s">
         <v>20</v>
       </c>
       <c r="D163" t="s">
-        <v>379</v>
+        <v>365</v>
       </c>
       <c r="E163" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="F163" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G163" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H163">
         <v>0</v>
@@ -7171,25 +7171,25 @@
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>389</v>
+        <v>375</v>
       </c>
       <c r="B164" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C164" t="s">
         <v>20</v>
       </c>
       <c r="D164" t="s">
-        <v>390</v>
+        <v>376</v>
       </c>
       <c r="E164" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="F164" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G164" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H164">
         <v>0</v>
@@ -7197,25 +7197,25 @@
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>391</v>
+        <v>377</v>
       </c>
       <c r="B165" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C165" t="s">
         <v>20</v>
       </c>
       <c r="D165" t="s">
-        <v>392</v>
+        <v>378</v>
       </c>
       <c r="E165" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="F165" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G165" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H165">
         <v>1</v>
@@ -7223,25 +7223,25 @@
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>393</v>
+        <v>379</v>
       </c>
       <c r="B166" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C166" t="s">
         <v>20</v>
       </c>
       <c r="D166" t="s">
-        <v>394</v>
+        <v>380</v>
       </c>
       <c r="E166" t="s">
-        <v>327</v>
+        <v>313</v>
       </c>
       <c r="F166" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G166" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H166">
         <v>0</v>
@@ -7249,25 +7249,25 @@
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>395</v>
+        <v>381</v>
       </c>
       <c r="B167" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C167" t="s">
         <v>20</v>
       </c>
       <c r="D167" t="s">
-        <v>396</v>
+        <v>382</v>
       </c>
       <c r="E167" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="F167" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G167" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H167">
         <v>1</v>
@@ -7275,25 +7275,25 @@
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>397</v>
+        <v>383</v>
       </c>
       <c r="B168" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C168" t="s">
         <v>20</v>
       </c>
       <c r="D168" t="s">
-        <v>398</v>
+        <v>384</v>
       </c>
       <c r="E168" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="F168" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G168" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H168">
         <v>1</v>
@@ -7301,25 +7301,25 @@
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>399</v>
+        <v>385</v>
       </c>
       <c r="B169" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C169" t="s">
         <v>20</v>
       </c>
       <c r="D169" t="s">
-        <v>400</v>
+        <v>386</v>
       </c>
       <c r="E169" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="F169" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G169" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H169">
         <v>0</v>
@@ -7327,25 +7327,25 @@
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>401</v>
+        <v>387</v>
       </c>
       <c r="B170" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C170" t="s">
         <v>20</v>
       </c>
       <c r="D170" t="s">
-        <v>402</v>
+        <v>388</v>
       </c>
       <c r="E170" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="F170" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G170" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H170">
         <v>0</v>
@@ -7353,25 +7353,25 @@
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>403</v>
+        <v>389</v>
       </c>
       <c r="B171" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C171" t="s">
         <v>20</v>
       </c>
       <c r="D171" t="s">
-        <v>404</v>
+        <v>390</v>
       </c>
       <c r="E171" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="F171" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G171" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H171">
         <v>1</v>
@@ -7379,25 +7379,25 @@
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>405</v>
+        <v>391</v>
       </c>
       <c r="B172" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C172" t="s">
         <v>10</v>
       </c>
       <c r="D172" t="s">
-        <v>406</v>
+        <v>392</v>
       </c>
       <c r="E172" t="s">
-        <v>407</v>
+        <v>393</v>
       </c>
       <c r="F172" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G172" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H172">
         <v>0</v>
@@ -7405,25 +7405,25 @@
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>408</v>
+        <v>394</v>
       </c>
       <c r="B173" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C173" t="s">
         <v>10</v>
       </c>
       <c r="D173" t="s">
-        <v>409</v>
+        <v>395</v>
       </c>
       <c r="E173" t="s">
-        <v>410</v>
+        <v>396</v>
       </c>
       <c r="F173" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G173" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H173">
         <v>0</v>
@@ -7431,25 +7431,25 @@
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>411</v>
+        <v>397</v>
       </c>
       <c r="B174" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C174" t="s">
         <v>10</v>
       </c>
       <c r="D174" t="s">
-        <v>412</v>
+        <v>398</v>
       </c>
       <c r="E174" t="s">
-        <v>413</v>
+        <v>399</v>
       </c>
       <c r="F174" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G174" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H174">
         <v>0</v>
@@ -7457,25 +7457,25 @@
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>414</v>
+        <v>400</v>
       </c>
       <c r="B175" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C175" t="s">
         <v>10</v>
       </c>
       <c r="D175" t="s">
-        <v>415</v>
+        <v>401</v>
       </c>
       <c r="E175" t="s">
-        <v>416</v>
+        <v>402</v>
       </c>
       <c r="F175" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G175" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H175">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>417</v>
+        <v>403</v>
       </c>
       <c r="B176" t="s">
-        <v>418</v>
+        <v>404</v>
       </c>
       <c r="C176" t="s">
         <v>20</v>
       </c>
       <c r="D176" t="s">
-        <v>419</v>
+        <v>405</v>
       </c>
       <c r="E176" t="s">
-        <v>420</v>
+        <v>406</v>
       </c>
       <c r="F176" t="s">
-        <v>421</v>
+        <v>407</v>
       </c>
       <c r="G176" t="s">
         <v>13</v>
@@ -7509,22 +7509,22 @@
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>422</v>
+        <v>408</v>
       </c>
       <c r="B177" t="s">
-        <v>418</v>
+        <v>404</v>
       </c>
       <c r="C177" t="s">
         <v>20</v>
       </c>
       <c r="D177" t="s">
-        <v>423</v>
+        <v>409</v>
       </c>
       <c r="E177" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="F177" t="s">
-        <v>421</v>
+        <v>407</v>
       </c>
       <c r="G177" t="s">
         <v>13</v>
@@ -7535,22 +7535,22 @@
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>425</v>
+        <v>411</v>
       </c>
       <c r="B178" t="s">
-        <v>418</v>
+        <v>404</v>
       </c>
       <c r="C178" t="s">
         <v>20</v>
       </c>
       <c r="D178" t="s">
-        <v>426</v>
+        <v>412</v>
       </c>
       <c r="E178" t="s">
-        <v>427</v>
+        <v>413</v>
       </c>
       <c r="F178" t="s">
-        <v>421</v>
+        <v>407</v>
       </c>
       <c r="G178" t="s">
         <v>13</v>
@@ -7561,22 +7561,22 @@
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>428</v>
+        <v>414</v>
       </c>
       <c r="B179" t="s">
-        <v>429</v>
+        <v>415</v>
       </c>
       <c r="C179" t="s">
         <v>20</v>
       </c>
       <c r="D179" t="s">
-        <v>430</v>
+        <v>416</v>
       </c>
       <c r="E179" t="s">
-        <v>431</v>
+        <v>417</v>
       </c>
       <c r="F179" t="s">
-        <v>421</v>
+        <v>407</v>
       </c>
       <c r="G179" t="s">
         <v>13</v>
@@ -7587,22 +7587,22 @@
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>432</v>
+        <v>418</v>
       </c>
       <c r="B180" t="s">
-        <v>429</v>
+        <v>415</v>
       </c>
       <c r="C180" t="s">
         <v>20</v>
       </c>
       <c r="D180" t="s">
-        <v>433</v>
+        <v>419</v>
       </c>
       <c r="E180" t="s">
-        <v>434</v>
+        <v>420</v>
       </c>
       <c r="F180" t="s">
-        <v>421</v>
+        <v>407</v>
       </c>
       <c r="G180" t="s">
         <v>13</v>
@@ -7613,22 +7613,22 @@
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>435</v>
+        <v>421</v>
       </c>
       <c r="B181" t="s">
-        <v>436</v>
+        <v>422</v>
       </c>
       <c r="C181" t="s">
         <v>20</v>
       </c>
       <c r="D181" t="s">
-        <v>437</v>
+        <v>423</v>
       </c>
       <c r="E181" t="s">
-        <v>438</v>
+        <v>424</v>
       </c>
       <c r="F181" t="s">
-        <v>439</v>
+        <v>425</v>
       </c>
       <c r="G181" t="s">
         <v>13</v>
@@ -7639,22 +7639,22 @@
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>440</v>
+        <v>426</v>
       </c>
       <c r="B182" t="s">
-        <v>436</v>
+        <v>422</v>
       </c>
       <c r="C182" t="s">
         <v>10</v>
       </c>
       <c r="D182" t="s">
-        <v>441</v>
+        <v>427</v>
       </c>
       <c r="E182" t="s">
-        <v>442</v>
+        <v>428</v>
       </c>
       <c r="F182" t="s">
-        <v>443</v>
+        <v>429</v>
       </c>
       <c r="G182" t="s">
         <v>13</v>
@@ -7665,25 +7665,25 @@
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>444</v>
+        <v>430</v>
       </c>
       <c r="B183" t="s">
-        <v>436</v>
+        <v>422</v>
       </c>
       <c r="C183" t="s">
         <v>20</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>431</v>
       </c>
       <c r="E183" t="s">
-        <v>446</v>
+        <v>432</v>
       </c>
       <c r="F183" t="s">
-        <v>447</v>
+        <v>433</v>
       </c>
       <c r="G183" t="s">
-        <v>448</v>
+        <v>434</v>
       </c>
       <c r="H183">
         <v>1</v>
@@ -7691,25 +7691,25 @@
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>436</v>
+        <v>422</v>
       </c>
       <c r="B184" t="s">
-        <v>436</v>
+        <v>422</v>
       </c>
       <c r="C184" t="s">
         <v>20</v>
       </c>
       <c r="D184" t="s">
-        <v>449</v>
+        <v>435</v>
       </c>
       <c r="E184" t="s">
-        <v>446</v>
+        <v>432</v>
       </c>
       <c r="F184" t="s">
-        <v>447</v>
+        <v>433</v>
       </c>
       <c r="G184" t="s">
-        <v>448</v>
+        <v>434</v>
       </c>
       <c r="H184">
         <v>1</v>
@@ -7717,25 +7717,25 @@
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>450</v>
+        <v>436</v>
       </c>
       <c r="B185" t="s">
-        <v>436</v>
+        <v>422</v>
       </c>
       <c r="C185" t="s">
         <v>20</v>
       </c>
       <c r="D185" t="s">
-        <v>451</v>
+        <v>437</v>
       </c>
       <c r="E185" t="s">
-        <v>446</v>
+        <v>432</v>
       </c>
       <c r="F185" t="s">
-        <v>447</v>
+        <v>433</v>
       </c>
       <c r="G185" t="s">
-        <v>448</v>
+        <v>434</v>
       </c>
       <c r="H185">
         <v>1</v>
@@ -7743,25 +7743,25 @@
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>452</v>
+        <v>438</v>
       </c>
       <c r="B186" t="s">
-        <v>436</v>
+        <v>422</v>
       </c>
       <c r="C186" t="s">
         <v>20</v>
       </c>
       <c r="D186" t="s">
-        <v>453</v>
+        <v>439</v>
       </c>
       <c r="E186" t="s">
-        <v>446</v>
+        <v>432</v>
       </c>
       <c r="F186" t="s">
-        <v>447</v>
+        <v>433</v>
       </c>
       <c r="G186" t="s">
-        <v>448</v>
+        <v>434</v>
       </c>
       <c r="H186">
         <v>1</v>
@@ -7769,25 +7769,25 @@
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>454</v>
+        <v>440</v>
       </c>
       <c r="B187" t="s">
-        <v>436</v>
+        <v>422</v>
       </c>
       <c r="C187" t="s">
         <v>20</v>
       </c>
       <c r="D187" t="s">
-        <v>455</v>
+        <v>441</v>
       </c>
       <c r="E187" t="s">
-        <v>446</v>
+        <v>432</v>
       </c>
       <c r="F187" t="s">
-        <v>447</v>
+        <v>433</v>
       </c>
       <c r="G187" t="s">
-        <v>448</v>
+        <v>434</v>
       </c>
       <c r="H187">
         <v>1</v>
@@ -7795,25 +7795,25 @@
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>456</v>
+        <v>442</v>
       </c>
       <c r="B188" t="s">
-        <v>436</v>
+        <v>422</v>
       </c>
       <c r="C188" t="s">
         <v>20</v>
       </c>
       <c r="D188" t="s">
-        <v>457</v>
+        <v>443</v>
       </c>
       <c r="E188" t="s">
-        <v>446</v>
+        <v>432</v>
       </c>
       <c r="F188" t="s">
-        <v>447</v>
+        <v>433</v>
       </c>
       <c r="G188" t="s">
-        <v>448</v>
+        <v>434</v>
       </c>
       <c r="H188">
         <v>1</v>
@@ -7821,25 +7821,25 @@
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>458</v>
+        <v>444</v>
       </c>
       <c r="B189" t="s">
-        <v>436</v>
+        <v>422</v>
       </c>
       <c r="C189" t="s">
         <v>20</v>
       </c>
       <c r="D189" t="s">
-        <v>459</v>
+        <v>445</v>
       </c>
       <c r="E189" t="s">
-        <v>460</v>
+        <v>446</v>
       </c>
       <c r="F189" t="s">
-        <v>447</v>
+        <v>433</v>
       </c>
       <c r="G189" t="s">
-        <v>448</v>
+        <v>434</v>
       </c>
       <c r="H189">
         <v>1</v>
@@ -7847,25 +7847,25 @@
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>461</v>
+        <v>447</v>
       </c>
       <c r="B190" t="s">
-        <v>436</v>
+        <v>422</v>
       </c>
       <c r="C190" t="s">
         <v>20</v>
       </c>
       <c r="D190" t="s">
-        <v>462</v>
+        <v>448</v>
       </c>
       <c r="E190" t="s">
-        <v>460</v>
+        <v>446</v>
       </c>
       <c r="F190" t="s">
-        <v>447</v>
+        <v>433</v>
       </c>
       <c r="G190" t="s">
-        <v>448</v>
+        <v>434</v>
       </c>
       <c r="H190">
         <v>1</v>
@@ -7873,25 +7873,25 @@
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
-        <v>463</v>
+        <v>449</v>
       </c>
       <c r="B191" t="s">
-        <v>436</v>
+        <v>422</v>
       </c>
       <c r="C191" t="s">
         <v>20</v>
       </c>
       <c r="D191" t="s">
-        <v>464</v>
+        <v>450</v>
       </c>
       <c r="E191" t="s">
-        <v>460</v>
+        <v>446</v>
       </c>
       <c r="F191" t="s">
-        <v>447</v>
+        <v>433</v>
       </c>
       <c r="G191" t="s">
-        <v>448</v>
+        <v>434</v>
       </c>
       <c r="H191">
         <v>1</v>
@@ -7899,25 +7899,25 @@
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
-        <v>465</v>
+        <v>451</v>
       </c>
       <c r="B192" t="s">
-        <v>436</v>
+        <v>422</v>
       </c>
       <c r="C192" t="s">
         <v>20</v>
       </c>
       <c r="D192" t="s">
-        <v>466</v>
+        <v>452</v>
       </c>
       <c r="E192" t="s">
-        <v>460</v>
+        <v>446</v>
       </c>
       <c r="F192" t="s">
-        <v>447</v>
+        <v>433</v>
       </c>
       <c r="G192" t="s">
-        <v>448</v>
+        <v>434</v>
       </c>
       <c r="H192">
         <v>1</v>
@@ -7925,25 +7925,25 @@
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>467</v>
+        <v>453</v>
       </c>
       <c r="B193" t="s">
-        <v>436</v>
+        <v>422</v>
       </c>
       <c r="C193" t="s">
         <v>20</v>
       </c>
       <c r="D193" t="s">
-        <v>468</v>
+        <v>454</v>
       </c>
       <c r="E193" t="s">
-        <v>460</v>
+        <v>446</v>
       </c>
       <c r="F193" t="s">
-        <v>447</v>
+        <v>433</v>
       </c>
       <c r="G193" t="s">
-        <v>448</v>
+        <v>434</v>
       </c>
       <c r="H193">
         <v>1</v>
@@ -7951,25 +7951,25 @@
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>469</v>
+        <v>455</v>
       </c>
       <c r="B194" t="s">
-        <v>436</v>
+        <v>422</v>
       </c>
       <c r="C194" t="s">
         <v>20</v>
       </c>
       <c r="D194" t="s">
-        <v>470</v>
+        <v>456</v>
       </c>
       <c r="E194" t="s">
-        <v>460</v>
+        <v>446</v>
       </c>
       <c r="F194" t="s">
-        <v>447</v>
+        <v>433</v>
       </c>
       <c r="G194" t="s">
-        <v>448</v>
+        <v>434</v>
       </c>
       <c r="H194">
         <v>1</v>
@@ -7977,25 +7977,25 @@
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>471</v>
+        <v>457</v>
       </c>
       <c r="B195" t="s">
-        <v>436</v>
+        <v>422</v>
       </c>
       <c r="C195" t="s">
-        <v>471</v>
+        <v>457</v>
       </c>
       <c r="D195" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="E195" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="F195" t="s">
         <v>12</v>
       </c>
       <c r="G195" t="s">
-        <v>448</v>
+        <v>434</v>
       </c>
       <c r="H195">
         <v>0</v>
@@ -8003,25 +8003,25 @@
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>472</v>
+        <v>458</v>
       </c>
       <c r="B196" t="s">
-        <v>436</v>
+        <v>422</v>
       </c>
       <c r="C196" t="s">
-        <v>471</v>
+        <v>457</v>
       </c>
       <c r="D196" t="s">
-        <v>473</v>
+        <v>459</v>
       </c>
       <c r="E196" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="F196" t="s">
         <v>12</v>
       </c>
       <c r="G196" t="s">
-        <v>448</v>
+        <v>434</v>
       </c>
       <c r="H196">
         <v>0</v>
@@ -8029,25 +8029,25 @@
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>474</v>
+        <v>460</v>
       </c>
       <c r="B197" t="s">
-        <v>436</v>
+        <v>422</v>
       </c>
       <c r="C197" t="s">
-        <v>471</v>
+        <v>457</v>
       </c>
       <c r="D197" t="s">
-        <v>475</v>
+        <v>461</v>
       </c>
       <c r="E197" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="F197" t="s">
         <v>12</v>
       </c>
       <c r="G197" t="s">
-        <v>448</v>
+        <v>434</v>
       </c>
       <c r="H197">
         <v>1</v>
@@ -8055,25 +8055,25 @@
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>477</v>
+        <v>463</v>
       </c>
       <c r="B198" t="s">
-        <v>436</v>
+        <v>422</v>
       </c>
       <c r="C198" t="s">
-        <v>478</v>
+        <v>464</v>
       </c>
       <c r="D198" t="s">
-        <v>479</v>
+        <v>465</v>
       </c>
       <c r="E198" t="s">
-        <v>480</v>
+        <v>466</v>
       </c>
       <c r="F198" t="s">
-        <v>210</v>
+        <v>196</v>
       </c>
       <c r="G198" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H198">
         <v>0</v>
@@ -8081,25 +8081,25 @@
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>481</v>
+        <v>467</v>
       </c>
       <c r="B199" t="s">
-        <v>436</v>
+        <v>422</v>
       </c>
       <c r="C199" t="s">
-        <v>478</v>
+        <v>464</v>
       </c>
       <c r="D199" t="s">
-        <v>482</v>
+        <v>468</v>
       </c>
       <c r="E199" t="s">
-        <v>479</v>
+        <v>465</v>
       </c>
       <c r="F199" t="s">
-        <v>210</v>
+        <v>196</v>
       </c>
       <c r="G199" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H199">
         <v>0</v>
@@ -8107,25 +8107,25 @@
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>483</v>
+        <v>469</v>
       </c>
       <c r="B200" t="s">
-        <v>436</v>
+        <v>422</v>
       </c>
       <c r="C200" t="s">
-        <v>478</v>
+        <v>464</v>
       </c>
       <c r="D200" t="s">
-        <v>482</v>
+        <v>468</v>
       </c>
       <c r="E200" t="s">
-        <v>480</v>
+        <v>466</v>
       </c>
       <c r="F200" t="s">
-        <v>210</v>
+        <v>196</v>
       </c>
       <c r="G200" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H200">
         <v>0</v>
@@ -8133,19 +8133,19 @@
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
-        <v>484</v>
+        <v>470</v>
       </c>
       <c r="B201" t="s">
-        <v>485</v>
+        <v>471</v>
       </c>
       <c r="C201" t="s">
         <v>20</v>
       </c>
       <c r="D201" t="s">
-        <v>486</v>
+        <v>472</v>
       </c>
       <c r="E201" t="s">
-        <v>487</v>
+        <v>473</v>
       </c>
       <c r="F201" t="s">
         <v>12</v>
@@ -8159,19 +8159,19 @@
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
-        <v>488</v>
+        <v>474</v>
       </c>
       <c r="B202" t="s">
-        <v>485</v>
+        <v>471</v>
       </c>
       <c r="C202" t="s">
         <v>20</v>
       </c>
       <c r="D202" t="s">
-        <v>489</v>
+        <v>475</v>
       </c>
       <c r="E202" t="s">
-        <v>490</v>
+        <v>476</v>
       </c>
       <c r="F202" t="s">
         <v>12</v>
@@ -8185,19 +8185,19 @@
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
-        <v>491</v>
+        <v>477</v>
       </c>
       <c r="B203" t="s">
-        <v>485</v>
+        <v>471</v>
       </c>
       <c r="C203" t="s">
         <v>20</v>
       </c>
       <c r="D203" t="s">
-        <v>492</v>
+        <v>478</v>
       </c>
       <c r="E203" t="s">
-        <v>486</v>
+        <v>472</v>
       </c>
       <c r="F203" t="s">
         <v>12</v>
@@ -8211,19 +8211,19 @@
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
-        <v>493</v>
+        <v>479</v>
       </c>
       <c r="B204" t="s">
-        <v>485</v>
+        <v>471</v>
       </c>
       <c r="C204" t="s">
         <v>20</v>
       </c>
       <c r="D204" t="s">
-        <v>494</v>
+        <v>480</v>
       </c>
       <c r="E204" t="s">
-        <v>486</v>
+        <v>472</v>
       </c>
       <c r="F204" t="s">
         <v>12</v>
@@ -8237,19 +8237,19 @@
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
-        <v>495</v>
+        <v>481</v>
       </c>
       <c r="B205" t="s">
-        <v>485</v>
+        <v>471</v>
       </c>
       <c r="C205" t="s">
         <v>20</v>
       </c>
       <c r="D205" t="s">
-        <v>496</v>
+        <v>482</v>
       </c>
       <c r="E205" t="s">
-        <v>486</v>
+        <v>472</v>
       </c>
       <c r="F205" t="s">
         <v>12</v>
@@ -8263,19 +8263,19 @@
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
-        <v>497</v>
+        <v>483</v>
       </c>
       <c r="B206" t="s">
-        <v>485</v>
+        <v>471</v>
       </c>
       <c r="C206" t="s">
         <v>20</v>
       </c>
       <c r="D206" t="s">
-        <v>498</v>
+        <v>484</v>
       </c>
       <c r="E206" t="s">
-        <v>486</v>
+        <v>472</v>
       </c>
       <c r="F206" t="s">
         <v>12</v>
@@ -8289,19 +8289,19 @@
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
-        <v>499</v>
+        <v>485</v>
       </c>
       <c r="B207" t="s">
-        <v>485</v>
+        <v>471</v>
       </c>
       <c r="C207" t="s">
         <v>20</v>
       </c>
       <c r="D207" t="s">
-        <v>492</v>
+        <v>478</v>
       </c>
       <c r="E207" t="s">
-        <v>500</v>
+        <v>486</v>
       </c>
       <c r="F207" t="s">
         <v>12</v>
@@ -8315,19 +8315,19 @@
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
-        <v>501</v>
+        <v>487</v>
       </c>
       <c r="B208" t="s">
-        <v>485</v>
+        <v>471</v>
       </c>
       <c r="C208" t="s">
         <v>20</v>
       </c>
       <c r="D208" t="s">
-        <v>494</v>
+        <v>480</v>
       </c>
       <c r="E208" t="s">
-        <v>502</v>
+        <v>488</v>
       </c>
       <c r="F208" t="s">
         <v>12</v>
@@ -8341,19 +8341,19 @@
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
-        <v>503</v>
+        <v>489</v>
       </c>
       <c r="B209" t="s">
-        <v>485</v>
+        <v>471</v>
       </c>
       <c r="C209" t="s">
         <v>20</v>
       </c>
       <c r="D209" t="s">
-        <v>496</v>
+        <v>482</v>
       </c>
       <c r="E209" t="s">
-        <v>504</v>
+        <v>490</v>
       </c>
       <c r="F209" t="s">
         <v>12</v>
@@ -8367,19 +8367,19 @@
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
-        <v>505</v>
+        <v>491</v>
       </c>
       <c r="B210" t="s">
-        <v>485</v>
+        <v>471</v>
       </c>
       <c r="C210" t="s">
         <v>20</v>
       </c>
       <c r="D210" t="s">
-        <v>498</v>
+        <v>484</v>
       </c>
       <c r="E210" t="s">
-        <v>506</v>
+        <v>492</v>
       </c>
       <c r="F210" t="s">
         <v>12</v>
@@ -8393,25 +8393,25 @@
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
-        <v>507</v>
+        <v>493</v>
       </c>
       <c r="B211" t="s">
-        <v>508</v>
+        <v>494</v>
       </c>
       <c r="C211" t="s">
         <v>20</v>
       </c>
       <c r="D211" t="s">
-        <v>509</v>
+        <v>495</v>
       </c>
       <c r="E211" t="s">
-        <v>510</v>
+        <v>496</v>
       </c>
       <c r="F211" t="s">
-        <v>511</v>
+        <v>497</v>
       </c>
       <c r="G211" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H211">
         <v>1</v>
@@ -8419,25 +8419,25 @@
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
-        <v>512</v>
+        <v>498</v>
       </c>
       <c r="B212" t="s">
-        <v>508</v>
+        <v>494</v>
       </c>
       <c r="C212" t="s">
         <v>20</v>
       </c>
       <c r="D212" t="s">
-        <v>513</v>
+        <v>499</v>
       </c>
       <c r="E212" t="s">
-        <v>514</v>
+        <v>500</v>
       </c>
       <c r="F212" t="s">
-        <v>511</v>
+        <v>497</v>
       </c>
       <c r="G212" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H212">
         <v>1</v>
@@ -8445,25 +8445,25 @@
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
-        <v>515</v>
+        <v>501</v>
       </c>
       <c r="B213" t="s">
-        <v>508</v>
+        <v>494</v>
       </c>
       <c r="C213" t="s">
         <v>20</v>
       </c>
       <c r="D213" t="s">
-        <v>516</v>
+        <v>502</v>
       </c>
       <c r="E213" t="s">
-        <v>517</v>
+        <v>503</v>
       </c>
       <c r="F213" t="s">
-        <v>511</v>
+        <v>497</v>
       </c>
       <c r="G213" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H213">
         <v>1</v>
@@ -8471,25 +8471,25 @@
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
-        <v>518</v>
+        <v>504</v>
       </c>
       <c r="B214" t="s">
-        <v>508</v>
+        <v>494</v>
       </c>
       <c r="C214" t="s">
         <v>20</v>
       </c>
       <c r="D214" t="s">
-        <v>519</v>
+        <v>505</v>
       </c>
       <c r="E214" t="s">
-        <v>520</v>
+        <v>506</v>
       </c>
       <c r="F214" t="s">
-        <v>511</v>
+        <v>497</v>
       </c>
       <c r="G214" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H214">
         <v>1</v>
@@ -8497,25 +8497,25 @@
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
-        <v>521</v>
+        <v>507</v>
       </c>
       <c r="B215" t="s">
-        <v>508</v>
+        <v>494</v>
       </c>
       <c r="C215" t="s">
         <v>10</v>
       </c>
       <c r="D215" t="s">
-        <v>521</v>
+        <v>507</v>
       </c>
       <c r="E215" t="s">
-        <v>522</v>
+        <v>508</v>
       </c>
       <c r="F215" t="s">
-        <v>511</v>
+        <v>497</v>
       </c>
       <c r="G215" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H215">
         <v>1</v>
@@ -8523,25 +8523,25 @@
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
-        <v>523</v>
+        <v>509</v>
       </c>
       <c r="B216" t="s">
-        <v>508</v>
+        <v>494</v>
       </c>
       <c r="C216" t="s">
         <v>20</v>
       </c>
       <c r="D216" t="s">
-        <v>524</v>
+        <v>510</v>
       </c>
       <c r="E216" t="s">
-        <v>525</v>
+        <v>511</v>
       </c>
       <c r="F216" t="s">
-        <v>511</v>
+        <v>497</v>
       </c>
       <c r="G216" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H216">
         <v>1</v>
@@ -8549,25 +8549,25 @@
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
-        <v>526</v>
+        <v>512</v>
       </c>
       <c r="B217" t="s">
-        <v>508</v>
+        <v>494</v>
       </c>
       <c r="C217" t="s">
         <v>20</v>
       </c>
       <c r="D217" t="s">
-        <v>527</v>
+        <v>513</v>
       </c>
       <c r="E217" t="s">
-        <v>528</v>
+        <v>514</v>
       </c>
       <c r="F217" t="s">
-        <v>511</v>
+        <v>497</v>
       </c>
       <c r="G217" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H217">
         <v>1</v>
@@ -8575,25 +8575,25 @@
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
-        <v>529</v>
+        <v>515</v>
       </c>
       <c r="B218" t="s">
-        <v>508</v>
+        <v>494</v>
       </c>
       <c r="C218" t="s">
         <v>20</v>
       </c>
       <c r="D218" t="s">
-        <v>530</v>
+        <v>516</v>
       </c>
       <c r="E218" t="s">
-        <v>531</v>
+        <v>517</v>
       </c>
       <c r="F218" t="s">
-        <v>511</v>
+        <v>497</v>
       </c>
       <c r="G218" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H218">
         <v>1</v>
@@ -8601,25 +8601,25 @@
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
-        <v>532</v>
+        <v>518</v>
       </c>
       <c r="B219" t="s">
-        <v>508</v>
+        <v>494</v>
       </c>
       <c r="C219" t="s">
         <v>20</v>
       </c>
       <c r="D219" t="s">
-        <v>533</v>
+        <v>519</v>
       </c>
       <c r="E219" t="s">
-        <v>534</v>
+        <v>520</v>
       </c>
       <c r="F219" t="s">
-        <v>511</v>
+        <v>497</v>
       </c>
       <c r="G219" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H219">
         <v>1</v>
@@ -8627,25 +8627,25 @@
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
-        <v>535</v>
+        <v>521</v>
       </c>
       <c r="B220" t="s">
-        <v>508</v>
+        <v>494</v>
       </c>
       <c r="C220" t="s">
         <v>20</v>
       </c>
       <c r="D220" t="s">
-        <v>536</v>
+        <v>522</v>
       </c>
       <c r="E220" t="s">
-        <v>537</v>
+        <v>523</v>
       </c>
       <c r="F220" t="s">
-        <v>511</v>
+        <v>497</v>
       </c>
       <c r="G220" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H220">
         <v>1</v>
@@ -8653,25 +8653,25 @@
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
-        <v>538</v>
+        <v>524</v>
       </c>
       <c r="B221" t="s">
-        <v>508</v>
+        <v>494</v>
       </c>
       <c r="C221" t="s">
         <v>20</v>
       </c>
       <c r="D221" t="s">
-        <v>539</v>
+        <v>525</v>
       </c>
       <c r="E221" t="s">
-        <v>540</v>
+        <v>526</v>
       </c>
       <c r="F221" t="s">
-        <v>511</v>
+        <v>497</v>
       </c>
       <c r="G221" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H221">
         <v>0</v>
@@ -8679,25 +8679,25 @@
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
-        <v>541</v>
+        <v>527</v>
       </c>
       <c r="B222" t="s">
-        <v>508</v>
+        <v>494</v>
       </c>
       <c r="C222" t="s">
         <v>20</v>
       </c>
       <c r="D222" t="s">
-        <v>542</v>
+        <v>528</v>
       </c>
       <c r="E222" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="F222" t="s">
-        <v>511</v>
+        <v>497</v>
       </c>
       <c r="G222" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H222">
         <v>0</v>
@@ -8705,25 +8705,25 @@
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>543</v>
+        <v>529</v>
       </c>
       <c r="B223" t="s">
-        <v>508</v>
+        <v>494</v>
       </c>
       <c r="C223" t="s">
         <v>20</v>
       </c>
       <c r="D223" t="s">
-        <v>542</v>
+        <v>528</v>
       </c>
       <c r="E223" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="F223" t="s">
-        <v>511</v>
+        <v>497</v>
       </c>
       <c r="G223" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H223">
         <v>0</v>
@@ -8731,25 +8731,25 @@
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="B224" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="C224" t="s">
         <v>20</v>
       </c>
       <c r="D224" t="s">
-        <v>208</v>
+        <v>194</v>
       </c>
       <c r="E224" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="F224" t="s">
-        <v>210</v>
+        <v>196</v>
       </c>
       <c r="G224" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H224">
         <v>0</v>
@@ -8757,25 +8757,25 @@
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="B225" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="C225" t="s">
         <v>20</v>
       </c>
       <c r="D225" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="E225" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="F225" t="s">
-        <v>210</v>
+        <v>196</v>
       </c>
       <c r="G225" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H225">
         <v>0</v>
@@ -8783,25 +8783,25 @@
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="B226" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="C226" t="s">
         <v>20</v>
       </c>
       <c r="D226" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="E226" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="F226" t="s">
-        <v>210</v>
+        <v>196</v>
       </c>
       <c r="G226" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H226">
         <v>0</v>
@@ -8809,25 +8809,25 @@
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="B227" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="C227" t="s">
         <v>20</v>
       </c>
       <c r="D227" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="E227">
         <v>1</v>
       </c>
       <c r="F227" t="s">
-        <v>210</v>
+        <v>196</v>
       </c>
       <c r="G227" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H227">
         <v>0</v>
@@ -8835,25 +8835,25 @@
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>544</v>
+        <v>530</v>
       </c>
       <c r="B228" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C228" t="s">
         <v>20</v>
       </c>
       <c r="D228" t="s">
-        <v>545</v>
+        <v>531</v>
       </c>
       <c r="E228" t="s">
-        <v>546</v>
+        <v>532</v>
       </c>
       <c r="F228" t="s">
-        <v>547</v>
+        <v>533</v>
       </c>
       <c r="G228" t="s">
-        <v>548</v>
+        <v>534</v>
       </c>
       <c r="H228">
         <v>0</v>
@@ -8861,25 +8861,25 @@
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
-        <v>549</v>
+        <v>535</v>
       </c>
       <c r="B229" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C229" t="s">
         <v>20</v>
       </c>
       <c r="D229" t="s">
-        <v>550</v>
+        <v>536</v>
       </c>
       <c r="E229" t="s">
-        <v>379</v>
+        <v>365</v>
       </c>
       <c r="F229" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G229" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H229">
         <v>0</v>
@@ -8887,25 +8887,25 @@
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
-        <v>551</v>
+        <v>537</v>
       </c>
       <c r="B230" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C230" t="s">
         <v>20</v>
       </c>
       <c r="D230" t="s">
-        <v>552</v>
+        <v>538</v>
       </c>
       <c r="E230" t="s">
-        <v>379</v>
+        <v>365</v>
       </c>
       <c r="F230" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G230" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H230">
         <v>0</v>
@@ -8913,25 +8913,25 @@
     </row>
     <row r="231" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
-        <v>553</v>
+        <v>539</v>
       </c>
       <c r="B231" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C231" t="s">
         <v>20</v>
       </c>
       <c r="D231" t="s">
-        <v>554</v>
+        <v>540</v>
       </c>
       <c r="E231" t="s">
-        <v>379</v>
+        <v>365</v>
       </c>
       <c r="F231" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G231" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H231">
         <v>0</v>
@@ -8939,25 +8939,25 @@
     </row>
     <row r="232" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
-        <v>555</v>
+        <v>541</v>
       </c>
       <c r="B232" t="s">
-        <v>556</v>
+        <v>542</v>
       </c>
       <c r="C232" t="s">
         <v>20</v>
       </c>
       <c r="D232" t="s">
-        <v>557</v>
+        <v>543</v>
       </c>
       <c r="E232" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="F232" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="G232" t="s">
-        <v>558</v>
+        <v>544</v>
       </c>
       <c r="H232">
         <v>0</v>
@@ -8965,25 +8965,25 @@
     </row>
     <row r="233" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
-        <v>559</v>
+        <v>545</v>
       </c>
       <c r="B233" t="s">
-        <v>556</v>
+        <v>542</v>
       </c>
       <c r="C233" t="s">
         <v>20</v>
       </c>
       <c r="D233" t="s">
-        <v>560</v>
+        <v>546</v>
       </c>
       <c r="E233" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="F233" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="G233" t="s">
-        <v>558</v>
+        <v>544</v>
       </c>
       <c r="H233">
         <v>0</v>
@@ -8991,25 +8991,25 @@
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
-        <v>561</v>
+        <v>547</v>
       </c>
       <c r="B234" t="s">
-        <v>556</v>
+        <v>542</v>
       </c>
       <c r="C234" t="s">
         <v>20</v>
       </c>
       <c r="D234" t="s">
-        <v>562</v>
+        <v>548</v>
       </c>
       <c r="E234" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="F234" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="G234" t="s">
-        <v>558</v>
+        <v>544</v>
       </c>
       <c r="H234">
         <v>0</v>
@@ -9017,25 +9017,25 @@
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
-        <v>563</v>
+        <v>549</v>
       </c>
       <c r="B235" t="s">
-        <v>556</v>
+        <v>542</v>
       </c>
       <c r="C235" t="s">
         <v>20</v>
       </c>
       <c r="D235" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="E235" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="F235" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="G235" t="s">
-        <v>558</v>
+        <v>544</v>
       </c>
       <c r="H235">
         <v>0</v>
@@ -9043,25 +9043,25 @@
     </row>
     <row r="236" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
-        <v>565</v>
+        <v>551</v>
       </c>
       <c r="B236" t="s">
-        <v>556</v>
+        <v>542</v>
       </c>
       <c r="C236" t="s">
         <v>20</v>
       </c>
       <c r="D236" t="s">
-        <v>566</v>
+        <v>552</v>
       </c>
       <c r="E236" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="F236" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="G236" t="s">
-        <v>558</v>
+        <v>544</v>
       </c>
       <c r="H236">
         <v>0</v>
@@ -9069,25 +9069,25 @@
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
-        <v>567</v>
+        <v>553</v>
       </c>
       <c r="B237" t="s">
-        <v>556</v>
+        <v>542</v>
       </c>
       <c r="C237" t="s">
         <v>20</v>
       </c>
       <c r="D237" t="s">
-        <v>568</v>
+        <v>554</v>
       </c>
       <c r="E237" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="F237" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="G237" t="s">
-        <v>558</v>
+        <v>544</v>
       </c>
       <c r="H237">
         <v>0</v>
@@ -9095,25 +9095,25 @@
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
-        <v>569</v>
+        <v>555</v>
       </c>
       <c r="B238" t="s">
+        <v>542</v>
+      </c>
+      <c r="C238" t="s">
+        <v>20</v>
+      </c>
+      <c r="D238" t="s">
         <v>556</v>
       </c>
-      <c r="C238" t="s">
-        <v>20</v>
-      </c>
-      <c r="D238" t="s">
-        <v>570</v>
-      </c>
       <c r="E238" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="F238" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="G238" t="s">
-        <v>558</v>
+        <v>544</v>
       </c>
       <c r="H238">
         <v>0</v>
@@ -9121,25 +9121,25 @@
     </row>
     <row r="239" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
-        <v>571</v>
+        <v>557</v>
       </c>
       <c r="B239" t="s">
-        <v>556</v>
+        <v>542</v>
       </c>
       <c r="C239" t="s">
         <v>20</v>
       </c>
       <c r="D239" t="s">
-        <v>572</v>
+        <v>558</v>
       </c>
       <c r="E239" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="F239" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="G239" t="s">
-        <v>558</v>
+        <v>544</v>
       </c>
       <c r="H239">
         <v>0</v>
@@ -9147,25 +9147,25 @@
     </row>
     <row r="240" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
-        <v>573</v>
+        <v>559</v>
       </c>
       <c r="B240" t="s">
-        <v>556</v>
+        <v>542</v>
       </c>
       <c r="C240" t="s">
         <v>20</v>
       </c>
       <c r="D240" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="E240" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="F240" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="G240" t="s">
-        <v>558</v>
+        <v>544</v>
       </c>
       <c r="H240">
         <v>0</v>
@@ -9173,25 +9173,25 @@
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
-        <v>575</v>
+        <v>561</v>
       </c>
       <c r="B241" t="s">
-        <v>556</v>
+        <v>542</v>
       </c>
       <c r="C241" t="s">
         <v>20</v>
       </c>
       <c r="D241" t="s">
-        <v>576</v>
+        <v>562</v>
       </c>
       <c r="E241" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="F241" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="G241" t="s">
-        <v>558</v>
+        <v>544</v>
       </c>
       <c r="H241">
         <v>0</v>
@@ -9199,25 +9199,25 @@
     </row>
     <row r="242" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
-        <v>577</v>
+        <v>563</v>
       </c>
       <c r="B242" t="s">
-        <v>556</v>
+        <v>542</v>
       </c>
       <c r="C242" t="s">
         <v>20</v>
       </c>
       <c r="D242" t="s">
-        <v>578</v>
+        <v>564</v>
       </c>
       <c r="E242" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="F242" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="G242" t="s">
-        <v>558</v>
+        <v>544</v>
       </c>
       <c r="H242">
         <v>0</v>
@@ -9225,25 +9225,25 @@
     </row>
     <row r="243" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
-        <v>579</v>
+        <v>565</v>
       </c>
       <c r="B243" t="s">
-        <v>556</v>
+        <v>542</v>
       </c>
       <c r="C243" t="s">
         <v>20</v>
       </c>
       <c r="D243" t="s">
-        <v>580</v>
+        <v>566</v>
       </c>
       <c r="E243" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="F243" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="G243" t="s">
-        <v>558</v>
+        <v>544</v>
       </c>
       <c r="H243">
         <v>0</v>
@@ -9251,25 +9251,25 @@
     </row>
     <row r="244" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
-        <v>581</v>
+        <v>567</v>
       </c>
       <c r="B244" t="s">
-        <v>556</v>
+        <v>542</v>
       </c>
       <c r="C244" t="s">
         <v>20</v>
       </c>
       <c r="D244" t="s">
-        <v>582</v>
+        <v>568</v>
       </c>
       <c r="E244" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="F244" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="G244" t="s">
-        <v>558</v>
+        <v>544</v>
       </c>
       <c r="H244">
         <v>0</v>
@@ -9277,25 +9277,25 @@
     </row>
     <row r="245" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
-        <v>583</v>
+        <v>569</v>
       </c>
       <c r="B245" t="s">
-        <v>556</v>
+        <v>542</v>
       </c>
       <c r="C245" t="s">
         <v>20</v>
       </c>
       <c r="D245" t="s">
-        <v>584</v>
+        <v>570</v>
       </c>
       <c r="E245" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="F245" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="G245" t="s">
-        <v>558</v>
+        <v>544</v>
       </c>
       <c r="H245">
         <v>0</v>
@@ -9303,25 +9303,25 @@
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
-        <v>585</v>
+        <v>571</v>
       </c>
       <c r="B246" t="s">
-        <v>556</v>
+        <v>542</v>
       </c>
       <c r="C246" t="s">
         <v>20</v>
       </c>
       <c r="D246" t="s">
-        <v>586</v>
+        <v>572</v>
       </c>
       <c r="E246" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="F246" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="G246" t="s">
-        <v>558</v>
+        <v>544</v>
       </c>
       <c r="H246">
         <v>0</v>
@@ -9329,25 +9329,25 @@
     </row>
     <row r="247" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
-        <v>587</v>
+        <v>573</v>
       </c>
       <c r="B247" t="s">
-        <v>556</v>
+        <v>542</v>
       </c>
       <c r="C247" t="s">
         <v>20</v>
       </c>
       <c r="D247" t="s">
-        <v>588</v>
+        <v>574</v>
       </c>
       <c r="E247" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="F247" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="G247" t="s">
-        <v>558</v>
+        <v>544</v>
       </c>
       <c r="H247">
         <v>0</v>
@@ -9355,25 +9355,25 @@
     </row>
     <row r="248" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
-        <v>589</v>
+        <v>575</v>
       </c>
       <c r="B248" t="s">
-        <v>556</v>
+        <v>542</v>
       </c>
       <c r="C248" t="s">
         <v>20</v>
       </c>
       <c r="D248" t="s">
-        <v>590</v>
+        <v>576</v>
       </c>
       <c r="E248" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="F248" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="G248" t="s">
-        <v>558</v>
+        <v>544</v>
       </c>
       <c r="H248">
         <v>0</v>
@@ -9381,25 +9381,25 @@
     </row>
     <row r="249" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
-        <v>591</v>
+        <v>577</v>
       </c>
       <c r="B249" t="s">
-        <v>556</v>
+        <v>542</v>
       </c>
       <c r="C249" t="s">
         <v>20</v>
       </c>
       <c r="D249" t="s">
-        <v>592</v>
+        <v>578</v>
       </c>
       <c r="E249" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="F249" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="G249" t="s">
-        <v>558</v>
+        <v>544</v>
       </c>
       <c r="H249">
         <v>0</v>
@@ -9407,25 +9407,25 @@
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="B250" t="s">
-        <v>556</v>
+        <v>542</v>
       </c>
       <c r="C250" t="s">
         <v>20</v>
       </c>
       <c r="D250" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="E250" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="F250" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="G250" t="s">
-        <v>558</v>
+        <v>544</v>
       </c>
       <c r="H250">
         <v>0</v>
@@ -9433,25 +9433,25 @@
     </row>
     <row r="251" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
-        <v>595</v>
+        <v>581</v>
       </c>
       <c r="B251" t="s">
-        <v>556</v>
+        <v>542</v>
       </c>
       <c r="C251" t="s">
         <v>20</v>
       </c>
       <c r="D251" t="s">
-        <v>596</v>
+        <v>582</v>
       </c>
       <c r="E251" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="F251" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="G251" t="s">
-        <v>558</v>
+        <v>544</v>
       </c>
       <c r="H251">
         <v>0</v>
@@ -9459,25 +9459,25 @@
     </row>
     <row r="252" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
-        <v>597</v>
+        <v>583</v>
       </c>
       <c r="B252" t="s">
-        <v>556</v>
+        <v>542</v>
       </c>
       <c r="C252" t="s">
         <v>20</v>
       </c>
       <c r="D252" t="s">
-        <v>598</v>
+        <v>584</v>
       </c>
       <c r="E252" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="F252" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="G252" t="s">
-        <v>558</v>
+        <v>544</v>
       </c>
       <c r="H252">
         <v>0</v>
@@ -9485,25 +9485,25 @@
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
-        <v>599</v>
+        <v>585</v>
       </c>
       <c r="B253" t="s">
-        <v>556</v>
+        <v>542</v>
       </c>
       <c r="C253" t="s">
         <v>20</v>
       </c>
       <c r="D253" t="s">
-        <v>600</v>
+        <v>586</v>
       </c>
       <c r="E253" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="F253" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="G253" t="s">
-        <v>558</v>
+        <v>544</v>
       </c>
       <c r="H253">
         <v>0</v>
@@ -9511,25 +9511,25 @@
     </row>
     <row r="254" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
-        <v>601</v>
+        <v>587</v>
       </c>
       <c r="B254" t="s">
-        <v>556</v>
+        <v>542</v>
       </c>
       <c r="C254" t="s">
         <v>20</v>
       </c>
       <c r="D254" t="s">
-        <v>602</v>
+        <v>588</v>
       </c>
       <c r="E254" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="F254" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="G254" t="s">
-        <v>558</v>
+        <v>544</v>
       </c>
       <c r="H254">
         <v>0</v>
@@ -9537,25 +9537,25 @@
     </row>
     <row r="255" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
-        <v>603</v>
+        <v>589</v>
       </c>
       <c r="B255" t="s">
-        <v>556</v>
+        <v>542</v>
       </c>
       <c r="C255" t="s">
         <v>20</v>
       </c>
       <c r="D255" t="s">
-        <v>604</v>
+        <v>590</v>
       </c>
       <c r="E255" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="F255" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="G255" t="s">
-        <v>558</v>
+        <v>544</v>
       </c>
       <c r="H255">
         <v>0</v>
@@ -9563,25 +9563,25 @@
     </row>
     <row r="256" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
-        <v>605</v>
+        <v>591</v>
       </c>
       <c r="B256" t="s">
-        <v>556</v>
+        <v>542</v>
       </c>
       <c r="C256" t="s">
         <v>20</v>
       </c>
       <c r="D256" t="s">
-        <v>606</v>
+        <v>592</v>
       </c>
       <c r="E256" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="F256" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="G256" t="s">
-        <v>558</v>
+        <v>544</v>
       </c>
       <c r="H256">
         <v>0</v>
@@ -9589,25 +9589,25 @@
     </row>
     <row r="257" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
-        <v>607</v>
+        <v>593</v>
       </c>
       <c r="B257" t="s">
-        <v>556</v>
+        <v>542</v>
       </c>
       <c r="C257" t="s">
         <v>20</v>
       </c>
       <c r="D257" t="s">
-        <v>608</v>
+        <v>594</v>
       </c>
       <c r="E257" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="F257" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="G257" t="s">
-        <v>558</v>
+        <v>544</v>
       </c>
       <c r="H257">
         <v>0</v>
@@ -9615,25 +9615,25 @@
     </row>
     <row r="258" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
-        <v>609</v>
+        <v>595</v>
       </c>
       <c r="B258" t="s">
-        <v>556</v>
+        <v>542</v>
       </c>
       <c r="C258" t="s">
         <v>20</v>
       </c>
       <c r="D258" t="s">
-        <v>610</v>
+        <v>596</v>
       </c>
       <c r="E258" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="F258" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="G258" t="s">
-        <v>558</v>
+        <v>544</v>
       </c>
       <c r="H258">
         <v>0</v>
@@ -9641,25 +9641,25 @@
     </row>
     <row r="259" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
-        <v>611</v>
+        <v>597</v>
       </c>
       <c r="B259" t="s">
-        <v>556</v>
+        <v>542</v>
       </c>
       <c r="C259" t="s">
         <v>20</v>
       </c>
       <c r="D259" t="s">
-        <v>612</v>
+        <v>598</v>
       </c>
       <c r="E259" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="F259" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="G259" t="s">
-        <v>558</v>
+        <v>544</v>
       </c>
       <c r="H259">
         <v>0</v>
@@ -9667,25 +9667,25 @@
     </row>
     <row r="260" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
-        <v>613</v>
+        <v>599</v>
       </c>
       <c r="B260" t="s">
-        <v>556</v>
+        <v>542</v>
       </c>
       <c r="C260" t="s">
         <v>20</v>
       </c>
       <c r="D260" t="s">
-        <v>614</v>
+        <v>600</v>
       </c>
       <c r="E260" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="F260" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="G260" t="s">
-        <v>558</v>
+        <v>544</v>
       </c>
       <c r="H260">
         <v>0</v>
@@ -9693,25 +9693,25 @@
     </row>
     <row r="261" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
-        <v>615</v>
+        <v>601</v>
       </c>
       <c r="B261" t="s">
-        <v>556</v>
+        <v>542</v>
       </c>
       <c r="C261" t="s">
         <v>20</v>
       </c>
       <c r="D261" t="s">
-        <v>616</v>
+        <v>602</v>
       </c>
       <c r="E261" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="F261" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="G261" t="s">
-        <v>558</v>
+        <v>544</v>
       </c>
       <c r="H261">
         <v>0</v>
@@ -9719,25 +9719,25 @@
     </row>
     <row r="262" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
-        <v>617</v>
+        <v>603</v>
       </c>
       <c r="B262" t="s">
-        <v>556</v>
+        <v>542</v>
       </c>
       <c r="C262" t="s">
         <v>20</v>
       </c>
       <c r="D262" t="s">
-        <v>618</v>
+        <v>604</v>
       </c>
       <c r="E262" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="F262" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="G262" t="s">
-        <v>558</v>
+        <v>544</v>
       </c>
       <c r="H262">
         <v>0</v>
@@ -9745,25 +9745,25 @@
     </row>
     <row r="263" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
-        <v>619</v>
+        <v>605</v>
       </c>
       <c r="B263" t="s">
-        <v>556</v>
+        <v>542</v>
       </c>
       <c r="C263" t="s">
         <v>20</v>
       </c>
       <c r="D263" t="s">
-        <v>620</v>
+        <v>606</v>
       </c>
       <c r="E263" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="F263" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="G263" t="s">
-        <v>558</v>
+        <v>544</v>
       </c>
       <c r="H263">
         <v>0</v>
@@ -9771,25 +9771,25 @@
     </row>
     <row r="264" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
-        <v>621</v>
+        <v>607</v>
       </c>
       <c r="B264" t="s">
-        <v>556</v>
+        <v>542</v>
       </c>
       <c r="C264" t="s">
         <v>20</v>
       </c>
       <c r="D264" t="s">
-        <v>622</v>
+        <v>608</v>
       </c>
       <c r="E264" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="F264" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="G264" t="s">
-        <v>558</v>
+        <v>544</v>
       </c>
       <c r="H264">
         <v>0</v>
@@ -9797,25 +9797,25 @@
     </row>
     <row r="265" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
-        <v>623</v>
+        <v>609</v>
       </c>
       <c r="B265" t="s">
-        <v>556</v>
+        <v>542</v>
       </c>
       <c r="C265" t="s">
         <v>20</v>
       </c>
       <c r="D265" t="s">
-        <v>624</v>
+        <v>610</v>
       </c>
       <c r="E265" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="F265" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="G265" t="s">
-        <v>558</v>
+        <v>544</v>
       </c>
       <c r="H265">
         <v>0</v>
@@ -9823,25 +9823,25 @@
     </row>
     <row r="266" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
-        <v>625</v>
+        <v>611</v>
       </c>
       <c r="B266" t="s">
-        <v>556</v>
+        <v>542</v>
       </c>
       <c r="C266" t="s">
         <v>20</v>
       </c>
       <c r="D266" t="s">
-        <v>626</v>
+        <v>612</v>
       </c>
       <c r="E266" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="F266" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="G266" t="s">
-        <v>558</v>
+        <v>544</v>
       </c>
       <c r="H266">
         <v>0</v>
@@ -9849,25 +9849,25 @@
     </row>
     <row r="267" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
-        <v>627</v>
+        <v>613</v>
       </c>
       <c r="B267" t="s">
-        <v>556</v>
+        <v>542</v>
       </c>
       <c r="C267" t="s">
         <v>20</v>
       </c>
       <c r="D267" t="s">
-        <v>628</v>
+        <v>614</v>
       </c>
       <c r="E267" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="F267" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="G267" t="s">
-        <v>558</v>
+        <v>544</v>
       </c>
       <c r="H267">
         <v>0</v>
@@ -9875,25 +9875,25 @@
     </row>
     <row r="268" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
-        <v>629</v>
+        <v>615</v>
       </c>
       <c r="B268" t="s">
-        <v>556</v>
+        <v>542</v>
       </c>
       <c r="C268" t="s">
         <v>20</v>
       </c>
       <c r="D268" t="s">
-        <v>630</v>
+        <v>616</v>
       </c>
       <c r="E268" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="F268" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="G268" t="s">
-        <v>558</v>
+        <v>544</v>
       </c>
       <c r="H268">
         <v>0</v>
@@ -9901,25 +9901,25 @@
     </row>
     <row r="269" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
-        <v>631</v>
+        <v>617</v>
       </c>
       <c r="B269" t="s">
-        <v>556</v>
+        <v>542</v>
       </c>
       <c r="C269" t="s">
         <v>20</v>
       </c>
       <c r="D269" t="s">
-        <v>632</v>
+        <v>618</v>
       </c>
       <c r="E269" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="F269" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="G269" t="s">
-        <v>558</v>
+        <v>544</v>
       </c>
       <c r="H269">
         <v>0</v>
@@ -9927,25 +9927,25 @@
     </row>
     <row r="270" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
-        <v>633</v>
+        <v>619</v>
       </c>
       <c r="B270" t="s">
-        <v>556</v>
+        <v>542</v>
       </c>
       <c r="C270" t="s">
         <v>20</v>
       </c>
       <c r="D270" t="s">
-        <v>634</v>
+        <v>620</v>
       </c>
       <c r="E270" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="F270" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="G270" t="s">
-        <v>558</v>
+        <v>544</v>
       </c>
       <c r="H270">
         <v>0</v>
@@ -9953,25 +9953,25 @@
     </row>
     <row r="271" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>635</v>
+        <v>621</v>
       </c>
       <c r="B271" t="s">
-        <v>556</v>
+        <v>542</v>
       </c>
       <c r="C271" t="s">
         <v>20</v>
       </c>
       <c r="D271" t="s">
-        <v>636</v>
+        <v>622</v>
       </c>
       <c r="E271" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="F271" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="G271" t="s">
-        <v>558</v>
+        <v>544</v>
       </c>
       <c r="H271">
         <v>0</v>
@@ -9979,25 +9979,25 @@
     </row>
     <row r="272" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
-        <v>637</v>
+        <v>623</v>
       </c>
       <c r="B272" t="s">
-        <v>556</v>
+        <v>542</v>
       </c>
       <c r="C272" t="s">
         <v>20</v>
       </c>
       <c r="D272" t="s">
-        <v>638</v>
+        <v>624</v>
       </c>
       <c r="E272" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="F272" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="G272" t="s">
-        <v>558</v>
+        <v>544</v>
       </c>
       <c r="H272">
         <v>0</v>
@@ -10005,25 +10005,25 @@
     </row>
     <row r="273" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
-        <v>639</v>
+        <v>625</v>
       </c>
       <c r="B273" t="s">
-        <v>556</v>
+        <v>542</v>
       </c>
       <c r="C273" t="s">
         <v>20</v>
       </c>
       <c r="D273" t="s">
-        <v>640</v>
+        <v>626</v>
       </c>
       <c r="E273" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="F273" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="G273" t="s">
-        <v>558</v>
+        <v>544</v>
       </c>
       <c r="H273">
         <v>0</v>
@@ -10031,25 +10031,25 @@
     </row>
     <row r="274" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
-        <v>641</v>
+        <v>627</v>
       </c>
       <c r="B274" t="s">
-        <v>556</v>
+        <v>542</v>
       </c>
       <c r="C274" t="s">
         <v>20</v>
       </c>
       <c r="D274" t="s">
-        <v>642</v>
+        <v>628</v>
       </c>
       <c r="E274" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="F274" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="G274" t="s">
-        <v>558</v>
+        <v>544</v>
       </c>
       <c r="H274">
         <v>0</v>
@@ -10057,25 +10057,25 @@
     </row>
     <row r="275" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>643</v>
+        <v>629</v>
       </c>
       <c r="B275" t="s">
-        <v>556</v>
+        <v>542</v>
       </c>
       <c r="C275" t="s">
         <v>20</v>
       </c>
       <c r="D275" t="s">
-        <v>644</v>
+        <v>630</v>
       </c>
       <c r="E275" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="F275" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="G275" t="s">
-        <v>558</v>
+        <v>544</v>
       </c>
       <c r="H275">
         <v>0</v>
@@ -10083,25 +10083,25 @@
     </row>
     <row r="276" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
-        <v>645</v>
+        <v>631</v>
       </c>
       <c r="B276" t="s">
-        <v>556</v>
+        <v>542</v>
       </c>
       <c r="C276" t="s">
         <v>20</v>
       </c>
       <c r="D276" t="s">
-        <v>646</v>
+        <v>632</v>
       </c>
       <c r="E276" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="F276" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="G276" t="s">
-        <v>558</v>
+        <v>544</v>
       </c>
       <c r="H276">
         <v>0</v>
@@ -10109,25 +10109,25 @@
     </row>
     <row r="277" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
-        <v>647</v>
+        <v>633</v>
       </c>
       <c r="B277" t="s">
-        <v>556</v>
+        <v>542</v>
       </c>
       <c r="C277" t="s">
         <v>20</v>
       </c>
       <c r="D277" t="s">
-        <v>648</v>
+        <v>634</v>
       </c>
       <c r="E277" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="F277" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="G277" t="s">
-        <v>558</v>
+        <v>544</v>
       </c>
       <c r="H277">
         <v>0</v>
@@ -10135,25 +10135,25 @@
     </row>
     <row r="278" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>649</v>
+        <v>635</v>
       </c>
       <c r="B278" t="s">
-        <v>556</v>
+        <v>542</v>
       </c>
       <c r="C278" t="s">
         <v>20</v>
       </c>
       <c r="D278" t="s">
-        <v>650</v>
+        <v>636</v>
       </c>
       <c r="E278" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="F278" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="G278" t="s">
-        <v>558</v>
+        <v>544</v>
       </c>
       <c r="H278">
         <v>1</v>

--- a/Inputs/idef.xlsx
+++ b/Inputs/idef.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sofia\Documents\BID\2025\calculo_indicators_R\Inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B75091E-F719-423D-AD8A-A0D4070DF87D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDBF4235-7DA8-4267-A656-A7544B6D625D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="10240" xr2:uid="{76C58BDB-E763-4EA4-A4AF-6A5E1AEAFFAC}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{76C58BDB-E763-4EA4-A4AF-6A5E1AEAFFAC}"/>
   </bookViews>
   <sheets>
     <sheet name="idef" sheetId="1" r:id="rId1"/>
@@ -18,12 +18,25 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">idef!$A$1:$H$278</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1946" uniqueCount="675">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1946" uniqueCount="676">
   <si>
     <t>indicator_name</t>
   </si>
@@ -2048,6 +2061,9 @@
   </si>
   <si>
     <t>razonesnoasis_ci == 4 &amp; edad_ci &gt;= 18 &amp; edad_ci &lt;= 24 &amp; asiste_ci != 1 &amp; nivel_edu&lt; 6</t>
+  </si>
+  <si>
+    <t>sex,age,quintile,area,ethnicity,disability,migration,isoalpha3,year</t>
   </si>
 </sst>
 </file>
@@ -2974,7 +2990,7 @@
         <v>656</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>675</v>
       </c>
       <c r="G2" t="s">
         <v>13</v>
@@ -3000,7 +3016,7 @@
         <v>660</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>675</v>
       </c>
       <c r="G3" t="s">
         <v>13</v>
@@ -3026,7 +3042,7 @@
         <v>659</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>675</v>
       </c>
       <c r="G4" t="s">
         <v>13</v>
@@ -3052,7 +3068,7 @@
         <v>658</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>675</v>
       </c>
       <c r="G5" t="s">
         <v>13</v>
@@ -3754,7 +3770,7 @@
         <v>79</v>
       </c>
       <c r="F32" t="s">
-        <v>12</v>
+        <v>675</v>
       </c>
       <c r="G32" t="s">
         <v>13</v>
@@ -3780,7 +3796,7 @@
         <v>79</v>
       </c>
       <c r="F33" t="s">
-        <v>12</v>
+        <v>675</v>
       </c>
       <c r="G33" t="s">
         <v>13</v>
@@ -3806,7 +3822,7 @@
         <v>79</v>
       </c>
       <c r="F34" t="s">
-        <v>12</v>
+        <v>675</v>
       </c>
       <c r="G34" t="s">
         <v>13</v>
@@ -3832,7 +3848,7 @@
         <v>79</v>
       </c>
       <c r="F35" t="s">
-        <v>12</v>
+        <v>675</v>
       </c>
       <c r="G35" t="s">
         <v>13</v>
@@ -3858,7 +3874,7 @@
         <v>79</v>
       </c>
       <c r="F36" t="s">
-        <v>12</v>
+        <v>675</v>
       </c>
       <c r="G36" t="s">
         <v>13</v>
@@ -3884,7 +3900,7 @@
         <v>79</v>
       </c>
       <c r="F37" t="s">
-        <v>12</v>
+        <v>675</v>
       </c>
       <c r="G37" t="s">
         <v>13</v>
@@ -3910,7 +3926,7 @@
         <v>79</v>
       </c>
       <c r="F38" t="s">
-        <v>12</v>
+        <v>675</v>
       </c>
       <c r="G38" t="s">
         <v>13</v>
@@ -3936,7 +3952,7 @@
         <v>79</v>
       </c>
       <c r="F39" t="s">
-        <v>12</v>
+        <v>675</v>
       </c>
       <c r="G39" t="s">
         <v>13</v>
@@ -3962,7 +3978,7 @@
         <v>79</v>
       </c>
       <c r="F40" t="s">
-        <v>12</v>
+        <v>675</v>
       </c>
       <c r="G40" t="s">
         <v>13</v>

--- a/Inputs/idef.xlsx
+++ b/Inputs/idef.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sofia\Documents\BID\2025\calculo_indicators_R\Inputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://idbg-my.sharepoint.com/personal/dcor_iadb_org/Documents/Documents/GitHub/calculo_indicators_R/Inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDBF4235-7DA8-4267-A656-A7544B6D625D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{DDBF4235-7DA8-4267-A656-A7544B6D625D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{589A2DC9-4C87-41C6-B79C-91E777BF8DDD}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{76C58BDB-E763-4EA4-A4AF-6A5E1AEAFFAC}"/>
   </bookViews>
@@ -2212,7 +2212,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2398,6 +2398,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -2559,9 +2565,10 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2974,106 +2981,106 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="2" t="s">
         <v>657</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="2" t="s">
         <v>656</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="A3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="2" t="s">
         <v>660</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="A4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="2" t="s">
         <v>659</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+      <c r="A5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="2" t="s">
         <v>658</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="2">
         <v>0</v>
       </c>
     </row>
@@ -3754,236 +3761,236 @@
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
+      <c r="A32" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C32" t="s">
-        <v>20</v>
-      </c>
-      <c r="D32" t="s">
+      <c r="C32" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D32" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="E32" t="s">
+      <c r="E32" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="F32" t="s">
+      <c r="F32" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="G32" t="s">
+      <c r="G32" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H32">
+      <c r="H32" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
+      <c r="A33" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C33" t="s">
-        <v>20</v>
-      </c>
-      <c r="D33" t="s">
+      <c r="C33" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D33" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="E33" t="s">
+      <c r="E33" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="F33" t="s">
+      <c r="F33" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="G33" t="s">
+      <c r="G33" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H33">
+      <c r="H33" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
+      <c r="A34" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C34" t="s">
-        <v>20</v>
-      </c>
-      <c r="D34" t="s">
+      <c r="C34" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D34" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E34" t="s">
+      <c r="E34" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="F34" t="s">
+      <c r="F34" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="G34" t="s">
+      <c r="G34" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H34">
+      <c r="H34" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
+      <c r="A35" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C35" t="s">
-        <v>20</v>
-      </c>
-      <c r="D35" t="s">
+      <c r="C35" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="E35" t="s">
+      <c r="E35" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="F35" t="s">
+      <c r="F35" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="G35" t="s">
+      <c r="G35" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H35">
+      <c r="H35" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
+      <c r="A36" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C36" t="s">
-        <v>20</v>
-      </c>
-      <c r="D36" t="s">
+      <c r="C36" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D36" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="E36" t="s">
+      <c r="E36" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="F36" t="s">
+      <c r="F36" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="G36" t="s">
+      <c r="G36" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H36">
+      <c r="H36" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
+      <c r="A37" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C37" t="s">
-        <v>20</v>
-      </c>
-      <c r="D37" t="s">
+      <c r="C37" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D37" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="E37" t="s">
+      <c r="E37" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="F37" t="s">
+      <c r="F37" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="G37" t="s">
+      <c r="G37" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H37">
+      <c r="H37" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
+      <c r="A38" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C38" t="s">
-        <v>20</v>
-      </c>
-      <c r="D38" t="s">
+      <c r="C38" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D38" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="E38" t="s">
+      <c r="E38" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="F38" t="s">
+      <c r="F38" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="G38" t="s">
+      <c r="G38" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H38">
+      <c r="H38" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
+      <c r="A39" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C39" t="s">
-        <v>20</v>
-      </c>
-      <c r="D39" t="s">
+      <c r="C39" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D39" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="E39" t="s">
+      <c r="E39" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="F39" t="s">
+      <c r="F39" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="G39" t="s">
+      <c r="G39" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H39">
+      <c r="H39" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A40" t="s">
+      <c r="A40" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C40" t="s">
-        <v>20</v>
-      </c>
-      <c r="D40" t="s">
+      <c r="C40" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D40" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="E40" t="s">
+      <c r="E40" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="F40" t="s">
+      <c r="F40" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="G40" t="s">
+      <c r="G40" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H40">
+      <c r="H40" s="2">
         <v>1</v>
       </c>
     </row>
@@ -4066,262 +4073,262 @@
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A44" t="s">
+      <c r="A44" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C44" t="s">
-        <v>20</v>
-      </c>
-      <c r="D44" t="s">
+      <c r="C44" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D44" s="2" t="s">
         <v>665</v>
       </c>
-      <c r="E44" t="s">
+      <c r="E44" s="2" t="s">
         <v>663</v>
       </c>
-      <c r="F44" t="s">
+      <c r="F44" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G44" t="s">
+      <c r="G44" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H44">
+      <c r="H44" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A45" t="s">
+      <c r="A45" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C45" t="s">
-        <v>20</v>
-      </c>
-      <c r="D45" t="s">
+      <c r="C45" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D45" s="2" t="s">
         <v>666</v>
       </c>
-      <c r="E45" t="s">
+      <c r="E45" s="2" t="s">
         <v>663</v>
       </c>
-      <c r="F45" t="s">
+      <c r="F45" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G45" t="s">
+      <c r="G45" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H45">
+      <c r="H45" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A46" t="s">
+      <c r="A46" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C46" t="s">
-        <v>20</v>
-      </c>
-      <c r="D46" t="s">
+      <c r="C46" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D46" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="E46" t="s">
+      <c r="E46" s="2" t="s">
         <v>663</v>
       </c>
-      <c r="F46" t="s">
+      <c r="F46" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G46" t="s">
+      <c r="G46" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H46">
+      <c r="H46" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
+      <c r="A47" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C47" t="s">
-        <v>20</v>
-      </c>
-      <c r="D47" t="s">
+      <c r="C47" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D47" s="2" t="s">
         <v>668</v>
       </c>
-      <c r="E47" t="s">
+      <c r="E47" s="2" t="s">
         <v>663</v>
       </c>
-      <c r="F47" t="s">
+      <c r="F47" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G47" t="s">
+      <c r="G47" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H47">
+      <c r="H47" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A48" t="s">
+      <c r="A48" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C48" t="s">
-        <v>20</v>
-      </c>
-      <c r="D48" t="s">
+      <c r="C48" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D48" s="2" t="s">
         <v>669</v>
       </c>
-      <c r="E48" t="s">
+      <c r="E48" s="2" t="s">
         <v>663</v>
       </c>
-      <c r="F48" t="s">
+      <c r="F48" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G48" t="s">
+      <c r="G48" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H48">
+      <c r="H48" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A49" t="s">
+      <c r="A49" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C49" t="s">
-        <v>20</v>
-      </c>
-      <c r="D49" t="s">
+      <c r="C49" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D49" s="2" t="s">
         <v>670</v>
       </c>
-      <c r="E49" t="s">
+      <c r="E49" s="2" t="s">
         <v>664</v>
       </c>
-      <c r="F49" t="s">
+      <c r="F49" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G49" t="s">
+      <c r="G49" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H49">
+      <c r="H49" s="2">
         <v>2</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A50" t="s">
+      <c r="A50" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C50" t="s">
-        <v>20</v>
-      </c>
-      <c r="D50" t="s">
+      <c r="C50" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D50" s="2" t="s">
         <v>671</v>
       </c>
-      <c r="E50" t="s">
+      <c r="E50" s="2" t="s">
         <v>664</v>
       </c>
-      <c r="F50" t="s">
+      <c r="F50" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G50" t="s">
+      <c r="G50" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H50">
+      <c r="H50" s="2">
         <v>3</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A51" t="s">
+      <c r="A51" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C51" t="s">
-        <v>20</v>
-      </c>
-      <c r="D51" t="s">
+      <c r="C51" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D51" s="2" t="s">
         <v>672</v>
       </c>
-      <c r="E51" t="s">
+      <c r="E51" s="2" t="s">
         <v>664</v>
       </c>
-      <c r="F51" t="s">
+      <c r="F51" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G51" t="s">
+      <c r="G51" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H51">
+      <c r="H51" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A52" t="s">
+      <c r="A52" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C52" t="s">
-        <v>20</v>
-      </c>
-      <c r="D52" t="s">
+      <c r="C52" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D52" s="2" t="s">
         <v>674</v>
       </c>
-      <c r="E52" t="s">
+      <c r="E52" s="2" t="s">
         <v>664</v>
       </c>
-      <c r="F52" t="s">
+      <c r="F52" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G52" t="s">
+      <c r="G52" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H52">
+      <c r="H52" s="2">
         <v>5</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A53" t="s">
+      <c r="A53" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C53" t="s">
-        <v>20</v>
-      </c>
-      <c r="D53" t="s">
+      <c r="C53" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D53" s="2" t="s">
         <v>673</v>
       </c>
-      <c r="E53" t="s">
+      <c r="E53" s="2" t="s">
         <v>664</v>
       </c>
-      <c r="F53" t="s">
+      <c r="F53" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G53" t="s">
+      <c r="G53" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H53">
+      <c r="H53" s="2">
         <v>6</v>
       </c>
     </row>

--- a/Inputs/idef.xlsx
+++ b/Inputs/idef.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://idbg-my.sharepoint.com/personal/dcor_iadb_org/Documents/Documents/GitHub/calculo_indicators_R/Inputs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://idbg-my.sharepoint.com/personal/matiasi_iadb_org/Documents/Documents/Github/calculo_indicators_R/Inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{DDBF4235-7DA8-4267-A656-A7544B6D625D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{589A2DC9-4C87-41C6-B79C-91E777BF8DDD}"/>
+  <xr:revisionPtr revIDLastSave="43" documentId="13_ncr:1_{DDBF4235-7DA8-4267-A656-A7544B6D625D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9FE2D5BD-A7CF-4353-B8C7-4BFC3035C5C2}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{76C58BDB-E763-4EA4-A4AF-6A5E1AEAFFAC}"/>
+    <workbookView xWindow="18705" yWindow="1995" windowWidth="16725" windowHeight="8355" xr2:uid="{76C58BDB-E763-4EA4-A4AF-6A5E1AEAFFAC}"/>
   </bookViews>
   <sheets>
     <sheet name="idef" sheetId="1" r:id="rId1"/>
@@ -2627,6 +2627,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2945,16 +2949,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D819304-4CBE-41FB-B05C-225E98C9F90E}">
   <dimension ref="A1:H278"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="51.1796875" customWidth="1"/>
-    <col min="5" max="5" width="88.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="51.140625" customWidth="1"/>
+    <col min="5" max="5" width="88.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2980,7 +2984,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -3006,7 +3010,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>14</v>
       </c>
@@ -3032,7 +3036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>16</v>
       </c>
@@ -3058,7 +3062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>18</v>
       </c>
@@ -3084,7 +3088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -3110,7 +3114,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>23</v>
       </c>
@@ -3136,7 +3140,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -3162,7 +3166,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>28</v>
       </c>
@@ -3188,7 +3192,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>31</v>
       </c>
@@ -3214,7 +3218,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>34</v>
       </c>
@@ -3240,7 +3244,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>37</v>
       </c>
@@ -3266,7 +3270,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>40</v>
       </c>
@@ -3292,7 +3296,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>42</v>
       </c>
@@ -3318,7 +3322,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>45</v>
       </c>
@@ -3344,7 +3348,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>48</v>
       </c>
@@ -3370,7 +3374,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>50</v>
       </c>
@@ -3396,7 +3400,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>52</v>
       </c>
@@ -3422,7 +3426,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>54</v>
       </c>
@@ -3448,7 +3452,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>638</v>
       </c>
@@ -3474,7 +3478,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>639</v>
       </c>
@@ -3500,7 +3504,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>653</v>
       </c>
@@ -3526,7 +3530,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>56</v>
       </c>
@@ -3552,7 +3556,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>58</v>
       </c>
@@ -3578,7 +3582,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>60</v>
       </c>
@@ -3604,7 +3608,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>62</v>
       </c>
@@ -3630,7 +3634,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>64</v>
       </c>
@@ -3656,7 +3660,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>68</v>
       </c>
@@ -3682,7 +3686,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>71</v>
       </c>
@@ -3708,7 +3712,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>73</v>
       </c>
@@ -3734,7 +3738,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>75</v>
       </c>
@@ -3760,7 +3764,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>77</v>
       </c>
@@ -3786,7 +3790,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>80</v>
       </c>
@@ -3812,7 +3816,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>82</v>
       </c>
@@ -3838,7 +3842,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>84</v>
       </c>
@@ -3864,7 +3868,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>86</v>
       </c>
@@ -3890,7 +3894,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>88</v>
       </c>
@@ -3916,7 +3920,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>90</v>
       </c>
@@ -3942,7 +3946,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>92</v>
       </c>
@@ -3968,7 +3972,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>94</v>
       </c>
@@ -3994,7 +3998,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>96</v>
       </c>
@@ -4020,7 +4024,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>98</v>
       </c>
@@ -4046,7 +4050,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>100</v>
       </c>
@@ -4072,7 +4076,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>102</v>
       </c>
@@ -4098,7 +4102,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>103</v>
       </c>
@@ -4124,7 +4128,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>104</v>
       </c>
@@ -4150,7 +4154,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>105</v>
       </c>
@@ -4176,7 +4180,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>106</v>
       </c>
@@ -4202,7 +4206,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>107</v>
       </c>
@@ -4228,7 +4232,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>108</v>
       </c>
@@ -4254,7 +4258,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>109</v>
       </c>
@@ -4280,7 +4284,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>110</v>
       </c>
@@ -4306,7 +4310,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>111</v>
       </c>
@@ -4332,7 +4336,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>112</v>
       </c>
@@ -4358,7 +4362,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>114</v>
       </c>
@@ -4384,7 +4388,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>119</v>
       </c>
@@ -4410,7 +4414,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>121</v>
       </c>
@@ -4436,7 +4440,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>123</v>
       </c>
@@ -4462,7 +4466,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>125</v>
       </c>
@@ -4488,7 +4492,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>128</v>
       </c>
@@ -4514,7 +4518,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>131</v>
       </c>
@@ -4540,7 +4544,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>134</v>
       </c>
@@ -4566,7 +4570,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>137</v>
       </c>
@@ -4592,7 +4596,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>140</v>
       </c>
@@ -4618,7 +4622,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>142</v>
       </c>
@@ -4644,7 +4648,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>145</v>
       </c>
@@ -4670,7 +4674,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>148</v>
       </c>
@@ -4696,7 +4700,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>151</v>
       </c>
@@ -4722,7 +4726,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>154</v>
       </c>
@@ -4748,7 +4752,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>158</v>
       </c>
@@ -4774,7 +4778,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>160</v>
       </c>
@@ -4800,7 +4804,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>163</v>
       </c>
@@ -4826,7 +4830,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>166</v>
       </c>
@@ -4852,7 +4856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>168</v>
       </c>
@@ -4878,7 +4882,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>172</v>
       </c>
@@ -4904,7 +4908,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>174</v>
       </c>
@@ -4930,7 +4934,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>176</v>
       </c>
@@ -4956,7 +4960,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>178</v>
       </c>
@@ -4982,7 +4986,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>180</v>
       </c>
@@ -5008,7 +5012,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>182</v>
       </c>
@@ -5034,7 +5038,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>186</v>
       </c>
@@ -5060,7 +5064,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>188</v>
       </c>
@@ -5086,7 +5090,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>190</v>
       </c>
@@ -5112,7 +5116,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>193</v>
       </c>
@@ -5138,7 +5142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>197</v>
       </c>
@@ -5164,7 +5168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>200</v>
       </c>
@@ -5190,7 +5194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>201</v>
       </c>
@@ -5216,7 +5220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>203</v>
       </c>
@@ -5242,7 +5246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>209</v>
       </c>
@@ -5268,7 +5272,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>212</v>
       </c>
@@ -5294,7 +5298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>215</v>
       </c>
@@ -5320,7 +5324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>216</v>
       </c>
@@ -5346,7 +5350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>219</v>
       </c>
@@ -5372,7 +5376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>222</v>
       </c>
@@ -5398,7 +5402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>225</v>
       </c>
@@ -5424,7 +5428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>228</v>
       </c>
@@ -5450,7 +5454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>230</v>
       </c>
@@ -5476,7 +5480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>232</v>
       </c>
@@ -5502,7 +5506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>234</v>
       </c>
@@ -5528,7 +5532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>235</v>
       </c>
@@ -5554,7 +5558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>236</v>
       </c>
@@ -5580,7 +5584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>239</v>
       </c>
@@ -5606,7 +5610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>242</v>
       </c>
@@ -5632,7 +5636,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>245</v>
       </c>
@@ -5658,7 +5662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>247</v>
       </c>
@@ -5684,7 +5688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>249</v>
       </c>
@@ -5710,7 +5714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>251</v>
       </c>
@@ -5736,7 +5740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>252</v>
       </c>
@@ -5762,7 +5766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>253</v>
       </c>
@@ -5788,7 +5792,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>256</v>
       </c>
@@ -5814,7 +5818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>259</v>
       </c>
@@ -5840,7 +5844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>261</v>
       </c>
@@ -5866,7 +5870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>263</v>
       </c>
@@ -5892,7 +5896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>266</v>
       </c>
@@ -5918,7 +5922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>268</v>
       </c>
@@ -5944,7 +5948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>271</v>
       </c>
@@ -5970,7 +5974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>274</v>
       </c>
@@ -5996,7 +6000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>277</v>
       </c>
@@ -6022,7 +6026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>279</v>
       </c>
@@ -6048,7 +6052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>282</v>
       </c>
@@ -6074,7 +6078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>284</v>
       </c>
@@ -6100,7 +6104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>286</v>
       </c>
@@ -6126,7 +6130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>288</v>
       </c>
@@ -6152,7 +6156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>290</v>
       </c>
@@ -6178,7 +6182,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>292</v>
       </c>
@@ -6204,7 +6208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>294</v>
       </c>
@@ -6230,7 +6234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>297</v>
       </c>
@@ -6256,7 +6260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>299</v>
       </c>
@@ -6282,7 +6286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>301</v>
       </c>
@@ -6308,7 +6312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>303</v>
       </c>
@@ -6334,7 +6338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>305</v>
       </c>
@@ -6360,7 +6364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>307</v>
       </c>
@@ -6386,7 +6390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>309</v>
       </c>
@@ -6412,7 +6416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>311</v>
       </c>
@@ -6438,7 +6442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>314</v>
       </c>
@@ -6464,7 +6468,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>316</v>
       </c>
@@ -6490,7 +6494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>318</v>
       </c>
@@ -6516,7 +6520,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>320</v>
       </c>
@@ -6542,7 +6546,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>322</v>
       </c>
@@ -6568,7 +6572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>325</v>
       </c>
@@ -6594,7 +6598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>327</v>
       </c>
@@ -6620,7 +6624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>329</v>
       </c>
@@ -6646,7 +6650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>331</v>
       </c>
@@ -6672,7 +6676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>334</v>
       </c>
@@ -6698,7 +6702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>337</v>
       </c>
@@ -6724,7 +6728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>339</v>
       </c>
@@ -6750,7 +6754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>340</v>
       </c>
@@ -6776,7 +6780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>342</v>
       </c>
@@ -6802,7 +6806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>344</v>
       </c>
@@ -6828,7 +6832,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>346</v>
       </c>
@@ -6854,7 +6858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>349</v>
       </c>
@@ -6880,7 +6884,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>351</v>
       </c>
@@ -6906,7 +6910,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>353</v>
       </c>
@@ -6932,7 +6936,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>355</v>
       </c>
@@ -6958,7 +6962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>357</v>
       </c>
@@ -6984,7 +6988,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>359</v>
       </c>
@@ -7010,7 +7014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>362</v>
       </c>
@@ -7036,7 +7040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>364</v>
       </c>
@@ -7062,7 +7066,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>366</v>
       </c>
@@ -7088,7 +7092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>368</v>
       </c>
@@ -7114,7 +7118,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>370</v>
       </c>
@@ -7140,7 +7144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>372</v>
       </c>
@@ -7166,7 +7170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>374</v>
       </c>
@@ -7192,7 +7196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>375</v>
       </c>
@@ -7218,7 +7222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>377</v>
       </c>
@@ -7244,7 +7248,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>379</v>
       </c>
@@ -7270,7 +7274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>381</v>
       </c>
@@ -7296,7 +7300,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>383</v>
       </c>
@@ -7322,7 +7326,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>385</v>
       </c>
@@ -7348,7 +7352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>387</v>
       </c>
@@ -7374,7 +7378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>389</v>
       </c>
@@ -7400,7 +7404,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>391</v>
       </c>
@@ -7426,7 +7430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>394</v>
       </c>
@@ -7452,7 +7456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>397</v>
       </c>
@@ -7478,7 +7482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>400</v>
       </c>
@@ -7504,7 +7508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>403</v>
       </c>
@@ -7530,7 +7534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>408</v>
       </c>
@@ -7556,7 +7560,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>411</v>
       </c>
@@ -7582,7 +7586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>414</v>
       </c>
@@ -7608,7 +7612,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>418</v>
       </c>
@@ -7634,7 +7638,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>421</v>
       </c>
@@ -7660,7 +7664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>426</v>
       </c>
@@ -7686,7 +7690,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>430</v>
       </c>
@@ -7712,7 +7716,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>422</v>
       </c>
@@ -7738,7 +7742,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>436</v>
       </c>
@@ -7764,7 +7768,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>438</v>
       </c>
@@ -7790,7 +7794,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>440</v>
       </c>
@@ -7816,7 +7820,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>442</v>
       </c>
@@ -7842,7 +7846,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>444</v>
       </c>
@@ -7868,7 +7872,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>447</v>
       </c>
@@ -7894,7 +7898,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>449</v>
       </c>
@@ -7920,7 +7924,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>451</v>
       </c>
@@ -7946,7 +7950,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>453</v>
       </c>
@@ -7972,7 +7976,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>455</v>
       </c>
@@ -7998,7 +8002,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>457</v>
       </c>
@@ -8024,7 +8028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>458</v>
       </c>
@@ -8050,7 +8054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>460</v>
       </c>
@@ -8076,7 +8080,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>463</v>
       </c>
@@ -8102,7 +8106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>467</v>
       </c>
@@ -8128,7 +8132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>469</v>
       </c>
@@ -8154,7 +8158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>470</v>
       </c>
@@ -8180,7 +8184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>474</v>
       </c>
@@ -8206,7 +8210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>477</v>
       </c>
@@ -8232,7 +8236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>479</v>
       </c>
@@ -8258,7 +8262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>481</v>
       </c>
@@ -8284,7 +8288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>483</v>
       </c>
@@ -8310,7 +8314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>485</v>
       </c>
@@ -8336,7 +8340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>487</v>
       </c>
@@ -8362,7 +8366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>489</v>
       </c>
@@ -8388,7 +8392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>491</v>
       </c>
@@ -8414,7 +8418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>493</v>
       </c>
@@ -8440,7 +8444,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>498</v>
       </c>
@@ -8466,7 +8470,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>501</v>
       </c>
@@ -8492,7 +8496,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>504</v>
       </c>
@@ -8518,7 +8522,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>507</v>
       </c>
@@ -8544,7 +8548,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>509</v>
       </c>
@@ -8570,7 +8574,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>512</v>
       </c>
@@ -8596,7 +8600,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>515</v>
       </c>
@@ -8622,7 +8626,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>518</v>
       </c>
@@ -8648,7 +8652,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>521</v>
       </c>
@@ -8674,7 +8678,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>524</v>
       </c>
@@ -8700,7 +8704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>527</v>
       </c>
@@ -8726,7 +8730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>529</v>
       </c>
@@ -8752,7 +8756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>193</v>
       </c>
@@ -8778,7 +8782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>197</v>
       </c>
@@ -8804,7 +8808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>200</v>
       </c>
@@ -8830,7 +8834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>201</v>
       </c>
@@ -8856,7 +8860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>530</v>
       </c>
@@ -8882,7 +8886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>535</v>
       </c>
@@ -8908,7 +8912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>537</v>
       </c>
@@ -8934,7 +8938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>539</v>
       </c>
@@ -8960,7 +8964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>541</v>
       </c>
@@ -8986,7 +8990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>545</v>
       </c>
@@ -9012,7 +9016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>547</v>
       </c>
@@ -9038,7 +9042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>549</v>
       </c>
@@ -9064,7 +9068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>551</v>
       </c>
@@ -9090,7 +9094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>553</v>
       </c>
@@ -9116,7 +9120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>555</v>
       </c>
@@ -9142,7 +9146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>557</v>
       </c>
@@ -9168,7 +9172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>559</v>
       </c>
@@ -9194,7 +9198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>561</v>
       </c>
@@ -9220,7 +9224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>563</v>
       </c>
@@ -9246,7 +9250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>565</v>
       </c>
@@ -9272,7 +9276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>567</v>
       </c>
@@ -9298,7 +9302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>569</v>
       </c>
@@ -9324,7 +9328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>571</v>
       </c>
@@ -9350,7 +9354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>573</v>
       </c>
@@ -9376,7 +9380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>575</v>
       </c>
@@ -9402,7 +9406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>577</v>
       </c>
@@ -9428,7 +9432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>579</v>
       </c>
@@ -9454,7 +9458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>581</v>
       </c>
@@ -9480,7 +9484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>583</v>
       </c>
@@ -9506,7 +9510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>585</v>
       </c>
@@ -9532,7 +9536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>587</v>
       </c>
@@ -9558,7 +9562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>589</v>
       </c>
@@ -9584,7 +9588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>591</v>
       </c>
@@ -9610,7 +9614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>593</v>
       </c>
@@ -9636,7 +9640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>595</v>
       </c>
@@ -9662,7 +9666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>597</v>
       </c>
@@ -9688,7 +9692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>599</v>
       </c>
@@ -9714,7 +9718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>601</v>
       </c>
@@ -9740,7 +9744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>603</v>
       </c>
@@ -9766,7 +9770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>605</v>
       </c>
@@ -9792,7 +9796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>607</v>
       </c>
@@ -9818,7 +9822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>609</v>
       </c>
@@ -9844,7 +9848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>611</v>
       </c>
@@ -9870,7 +9874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>613</v>
       </c>
@@ -9896,7 +9900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>615</v>
       </c>
@@ -9922,7 +9926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>617</v>
       </c>
@@ -9948,7 +9952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>619</v>
       </c>
@@ -9974,7 +9978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>621</v>
       </c>
@@ -10000,7 +10004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>623</v>
       </c>
@@ -10026,7 +10030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>625</v>
       </c>
@@ -10052,7 +10056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>627</v>
       </c>
@@ -10078,7 +10082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>629</v>
       </c>
@@ -10104,7 +10108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>631</v>
       </c>
@@ -10130,7 +10134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>633</v>
       </c>
@@ -10156,7 +10160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>635</v>
       </c>
@@ -10183,7 +10187,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H278" xr:uid="{3D819304-4CBE-41FB-B05C-225E98C9F90E}"/>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
